--- a/Juli-2026.xlsx
+++ b/Juli-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EEBBD2-660F-4F29-8C6F-F84DBF15009A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA9EF5A-7E17-415E-AA66-689F20051753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,16 +566,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>112</v>
+        <v>267</v>
       </c>
       <c r="C2" s="4">
-        <v>305</v>
+        <v>542</v>
       </c>
       <c r="D2" s="9">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E2" s="13">
-        <v>3.25</v>
+        <v>4.6363636363636367</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -585,16 +585,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>115</v>
+        <v>247</v>
       </c>
       <c r="C3" s="4">
-        <v>234</v>
+        <v>485</v>
       </c>
       <c r="D3" s="9">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E3" s="13">
-        <v>1.75</v>
+        <v>3.8181818181818183</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -604,16 +604,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>111</v>
+        <v>305</v>
       </c>
       <c r="C4" s="4">
-        <v>323</v>
+        <v>722</v>
       </c>
       <c r="D4" s="9">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E4" s="13">
-        <v>2</v>
+        <v>3.7272727272727271</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>61</v>
+        <v>256</v>
       </c>
       <c r="C5" s="4">
-        <v>199</v>
+        <v>534</v>
       </c>
       <c r="D5" s="9">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E5" s="13">
-        <v>2</v>
+        <v>4.2727272727272725</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -642,16 +642,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C6" s="4">
-        <v>310</v>
+        <v>481</v>
       </c>
       <c r="D6" s="9">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E6" s="13">
-        <v>3.75</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -661,16 +661,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>113</v>
+        <v>331</v>
       </c>
       <c r="C7" s="4">
-        <v>295</v>
+        <v>617</v>
       </c>
       <c r="D7" s="9">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="E7" s="13">
-        <v>3</v>
+        <v>5.8181818181818183</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -680,16 +680,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>90</v>
+        <v>291</v>
       </c>
       <c r="C8" s="4">
-        <v>247</v>
+        <v>608</v>
       </c>
       <c r="D8" s="9">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="E8" s="13">
-        <v>2</v>
+        <v>5.2727272727272725</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -699,16 +699,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="C9" s="4">
-        <v>387</v>
+        <v>730</v>
       </c>
       <c r="D9" s="9">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="E9" s="13">
-        <v>1.75</v>
+        <v>3.9090909090909092</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -718,16 +718,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>143</v>
+        <v>277</v>
       </c>
       <c r="C10" s="4">
-        <v>277</v>
+        <v>568</v>
       </c>
       <c r="D10" s="9">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E10" s="13">
-        <v>4.5</v>
+        <v>3.5454545454545454</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -737,16 +737,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>58</v>
+        <v>166</v>
       </c>
       <c r="C11" s="4">
-        <v>281</v>
+        <v>554</v>
       </c>
       <c r="D11" s="9">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E11" s="13">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -756,16 +756,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>109</v>
+        <v>272</v>
       </c>
       <c r="C12" s="4">
-        <v>358</v>
+        <v>548</v>
       </c>
       <c r="D12" s="9">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E12" s="13">
-        <v>2.5</v>
+        <v>3.2727272727272729</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -775,16 +775,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="C13" s="4">
-        <v>286</v>
+        <v>651</v>
       </c>
       <c r="D13" s="9">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E13" s="13">
-        <v>2.5</v>
+        <v>3.0909090909090908</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -794,16 +794,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="C14" s="4">
-        <v>247</v>
+        <v>563</v>
       </c>
       <c r="D14" s="9">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E14" s="13">
-        <v>0.75</v>
+        <v>2.2727272727272729</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -813,16 +813,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>70</v>
+        <v>185</v>
       </c>
       <c r="C15" s="4">
-        <v>358</v>
+        <v>754</v>
       </c>
       <c r="D15" s="9">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E15" s="13">
-        <v>1.5</v>
+        <v>2.5454545454545454</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -832,16 +832,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="C16" s="4">
-        <v>264</v>
+        <v>549</v>
       </c>
       <c r="D16" s="9">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E16" s="13">
-        <v>1.25</v>
+        <v>2.2727272727272729</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -851,16 +851,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="C17" s="4">
-        <v>326</v>
+        <v>689</v>
       </c>
       <c r="D17" s="9">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="E17" s="13">
-        <v>1.25</v>
+        <v>3.7272727272727271</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -870,16 +870,16 @@
         <v>22</v>
       </c>
       <c r="B18" s="6">
-        <v>1491</v>
+        <v>3830</v>
       </c>
       <c r="C18" s="6">
-        <v>4697</v>
+        <v>9595</v>
       </c>
       <c r="D18" s="10">
-        <v>144</v>
+        <v>645</v>
       </c>
       <c r="E18" s="14">
-        <v>2.25</v>
+        <v>3.6647727272727271</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -961,8 +961,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="7" bestFit="1" customWidth="1"/>
     <col min="12" max="31" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="7.42578125" customWidth="1"/>
     <col min="33" max="33" width="11.140625" bestFit="1" customWidth="1"/>
@@ -1089,13 +1090,25 @@
       <c r="G2" s="4">
         <v>119</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="H2" s="4">
+        <v>104</v>
+      </c>
+      <c r="I2" s="4">
+        <v>96</v>
+      </c>
+      <c r="J2" s="4">
+        <v>89</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
       <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="N2" s="4">
+        <v>103</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -1115,7 +1128,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>417</v>
+        <v>809</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1138,13 +1151,25 @@
       <c r="G3" s="4">
         <v>85</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="H3" s="4">
+        <v>96</v>
+      </c>
+      <c r="I3" s="4">
+        <v>84</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>120</v>
+      </c>
+      <c r="L3" s="4">
+        <v>83</v>
+      </c>
       <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -1164,7 +1189,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>349</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1187,13 +1212,25 @@
       <c r="G4" s="4">
         <v>18</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="H4" s="4">
+        <v>135</v>
+      </c>
+      <c r="I4" s="4">
+        <v>111</v>
+      </c>
+      <c r="J4" s="4">
+        <v>112</v>
+      </c>
+      <c r="K4" s="4">
+        <v>115</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
       <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="N4" s="4">
+        <v>120</v>
+      </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
@@ -1213,7 +1250,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>434</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1236,13 +1273,25 @@
       <c r="G5" s="4">
         <v>0</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="H5" s="4">
+        <v>105</v>
+      </c>
+      <c r="I5" s="4">
+        <v>102</v>
+      </c>
+      <c r="J5" s="4">
+        <v>105</v>
+      </c>
+      <c r="K5" s="4">
+        <v>118</v>
+      </c>
+      <c r="L5" s="4">
+        <v>100</v>
+      </c>
       <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
@@ -1262,7 +1311,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>260</v>
+        <v>790</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1285,13 +1334,25 @@
       <c r="G6" s="4">
         <v>95</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>98</v>
+      </c>
+      <c r="K6" s="4">
+        <v>64</v>
+      </c>
+      <c r="L6" s="4">
+        <v>105</v>
+      </c>
       <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
@@ -1311,7 +1372,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>437</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1334,13 +1395,25 @@
       <c r="G7" s="4">
         <v>125</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>118</v>
+      </c>
+      <c r="J7" s="4">
+        <v>98</v>
+      </c>
+      <c r="K7" s="4">
+        <v>111</v>
+      </c>
+      <c r="L7" s="4">
+        <v>95</v>
+      </c>
       <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
+      <c r="N7" s="4">
+        <v>118</v>
+      </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
@@ -1360,7 +1433,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>408</v>
+        <v>948</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1383,13 +1456,25 @@
       <c r="G8" s="4">
         <v>0</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="H8" s="4">
+        <v>138</v>
+      </c>
+      <c r="I8" s="4">
+        <v>114</v>
+      </c>
+      <c r="J8" s="4">
+        <v>111</v>
+      </c>
+      <c r="K8" s="4">
+        <v>104</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
       <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
+      <c r="N8" s="4">
+        <v>95</v>
+      </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
@@ -1409,7 +1494,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>337</v>
+        <v>899</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1432,13 +1517,25 @@
       <c r="G9" s="4">
         <v>107</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
+      <c r="H9" s="4">
+        <v>117</v>
+      </c>
+      <c r="I9" s="4">
+        <v>103</v>
+      </c>
+      <c r="J9" s="4">
+        <v>92</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>88</v>
+      </c>
       <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="N9" s="4">
+        <v>106</v>
+      </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
@@ -1458,7 +1555,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>478</v>
+        <v>984</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1481,13 +1578,25 @@
       <c r="G10" s="4">
         <v>99</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <v>111</v>
+      </c>
+      <c r="K10" s="4">
+        <v>106</v>
+      </c>
+      <c r="L10" s="4">
+        <v>105</v>
+      </c>
       <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+      <c r="N10" s="4">
+        <v>103</v>
+      </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
@@ -1507,7 +1616,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>420</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1530,13 +1639,25 @@
       <c r="G11" s="4">
         <v>78</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
+      <c r="H11" s="4">
+        <v>67</v>
+      </c>
+      <c r="I11" s="4">
+        <v>67</v>
+      </c>
+      <c r="J11" s="4">
+        <v>65</v>
+      </c>
+      <c r="K11" s="4">
+        <v>81</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
       <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
+      <c r="N11" s="4">
+        <v>101</v>
+      </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
@@ -1556,7 +1677,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>339</v>
+        <v>720</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1579,13 +1700,25 @@
       <c r="G12" s="4">
         <v>113</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
+      <c r="H12" s="4">
+        <v>113</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>106</v>
+      </c>
+      <c r="K12" s="4">
+        <v>109</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
       <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
+      <c r="N12" s="4">
+        <v>25</v>
+      </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
@@ -1605,7 +1738,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>467</v>
+        <v>820</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1628,13 +1761,25 @@
       <c r="G13" s="4">
         <v>82</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
+      <c r="H13" s="4">
+        <v>96</v>
+      </c>
+      <c r="I13" s="4">
+        <v>100</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>106</v>
+      </c>
+      <c r="L13" s="4">
+        <v>67</v>
+      </c>
       <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
+      <c r="N13" s="4">
+        <v>133</v>
+      </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -1654,7 +1799,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>369</v>
+        <v>871</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1677,13 +1822,25 @@
       <c r="G14" s="4">
         <v>0</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
+      <c r="H14" s="4">
+        <v>96</v>
+      </c>
+      <c r="I14" s="4">
+        <v>98</v>
+      </c>
+      <c r="J14" s="4">
+        <v>106</v>
+      </c>
+      <c r="K14" s="4">
+        <v>104</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
       <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
@@ -1703,7 +1860,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>305</v>
+        <v>709</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -1726,13 +1883,25 @@
       <c r="G15" s="4">
         <v>106</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
+      <c r="H15" s="4">
+        <v>113</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>96</v>
+      </c>
+      <c r="K15" s="4">
+        <v>101</v>
+      </c>
+      <c r="L15" s="4">
+        <v>96</v>
+      </c>
       <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
+      <c r="N15" s="4">
+        <v>105</v>
+      </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
@@ -1752,7 +1921,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>428</v>
+        <v>939</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -1775,13 +1944,25 @@
       <c r="G16" s="4">
         <v>111</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
+      <c r="H16" s="4">
+        <v>104</v>
+      </c>
+      <c r="I16" s="4">
+        <v>80</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>95</v>
+      </c>
+      <c r="L16" s="4">
+        <v>84</v>
+      </c>
       <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
@@ -1801,7 +1982,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>330</v>
+        <v>693</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -1824,13 +2005,25 @@
       <c r="G17" s="4">
         <v>106</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
+      <c r="H17" s="4">
+        <v>98</v>
+      </c>
+      <c r="I17" s="4">
+        <v>99</v>
+      </c>
+      <c r="J17" s="4">
+        <v>103</v>
+      </c>
+      <c r="K17" s="4">
+        <v>106</v>
+      </c>
+      <c r="L17" s="4">
+        <v>0</v>
+      </c>
       <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
+      <c r="N17" s="4">
+        <v>118</v>
+      </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -1850,7 +2043,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>410</v>
+        <v>934</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -1873,13 +2066,25 @@
       <c r="G18" s="6">
         <v>1244</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="H18" s="6">
+        <v>1383</v>
+      </c>
+      <c r="I18" s="6">
+        <v>1172</v>
+      </c>
+      <c r="J18" s="6">
+        <v>1292</v>
+      </c>
+      <c r="K18" s="6">
+        <v>1440</v>
+      </c>
+      <c r="L18" s="6">
+        <v>823</v>
+      </c>
       <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
+      <c r="N18" s="6">
+        <v>1127</v>
+      </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
@@ -1899,7 +2104,7 @@
       <c r="AE18" s="6"/>
       <c r="AF18" s="6"/>
       <c r="AG18" s="10">
-        <v>6188</v>
+        <v>13425</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -1972,7 +2177,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.25</v>
+        <v>3.6647727272727271</v>
       </c>
     </row>
   </sheetData>

--- a/Juli-2026.xlsx
+++ b/Juli-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA9EF5A-7E17-415E-AA66-689F20051753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F0707B-C049-430D-996E-E04C6D784849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,16 +566,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>267</v>
+        <v>312</v>
       </c>
       <c r="C2" s="4">
-        <v>542</v>
+        <v>621</v>
       </c>
       <c r="D2" s="9">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E2" s="13">
-        <v>4.6363636363636367</v>
+        <v>3.5</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -585,16 +585,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="C3" s="4">
-        <v>485</v>
+        <v>584</v>
       </c>
       <c r="D3" s="9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3" s="13">
-        <v>3.8181818181818183</v>
+        <v>3.1428571428571428</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -604,16 +604,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>305</v>
+        <v>348</v>
       </c>
       <c r="C4" s="4">
-        <v>722</v>
+        <v>860</v>
       </c>
       <c r="D4" s="9">
         <v>41</v>
       </c>
       <c r="E4" s="13">
-        <v>3.7272727272727271</v>
+        <v>2.9285714285714284</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="C5" s="4">
-        <v>534</v>
+        <v>567</v>
       </c>
       <c r="D5" s="9">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5" s="13">
-        <v>4.2727272727272725</v>
+        <v>3.2142857142857144</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -642,16 +642,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="C6" s="4">
-        <v>481</v>
+        <v>630</v>
       </c>
       <c r="D6" s="9">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E6" s="13">
-        <v>3.4545454545454546</v>
+        <v>3.3571428571428572</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -661,16 +661,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>331</v>
+        <v>422</v>
       </c>
       <c r="C7" s="4">
-        <v>617</v>
+        <v>749</v>
       </c>
       <c r="D7" s="9">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E7" s="13">
-        <v>5.8181818181818183</v>
+        <v>5.1428571428571432</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -680,16 +680,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="C8" s="4">
-        <v>608</v>
+        <v>724</v>
       </c>
       <c r="D8" s="9">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E8" s="13">
-        <v>5.2727272727272725</v>
+        <v>4.4285714285714288</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -699,16 +699,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="C9" s="4">
-        <v>730</v>
+        <v>855</v>
       </c>
       <c r="D9" s="9">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E9" s="13">
-        <v>3.9090909090909092</v>
+        <v>3.5</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -718,16 +718,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>277</v>
+        <v>334</v>
       </c>
       <c r="C10" s="4">
-        <v>568</v>
+        <v>652</v>
       </c>
       <c r="D10" s="9">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E10" s="13">
-        <v>3.5454545454545454</v>
+        <v>3.0714285714285716</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -737,16 +737,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="C11" s="4">
-        <v>554</v>
+        <v>606</v>
       </c>
       <c r="D11" s="9">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E11" s="13">
-        <v>3</v>
+        <v>2.5714285714285716</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -756,16 +756,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>272</v>
+        <v>380</v>
       </c>
       <c r="C12" s="4">
-        <v>548</v>
+        <v>666</v>
       </c>
       <c r="D12" s="9">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E12" s="13">
-        <v>3.2727272727272729</v>
+        <v>2.9285714285714284</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -775,16 +775,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="C13" s="4">
-        <v>651</v>
+        <v>677</v>
       </c>
       <c r="D13" s="9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" s="13">
-        <v>3.0909090909090908</v>
+        <v>2.2857142857142856</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -794,16 +794,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="C14" s="4">
-        <v>563</v>
+        <v>642</v>
       </c>
       <c r="D14" s="9">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E14" s="13">
-        <v>2.2727272727272729</v>
+        <v>1.6428571428571428</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -813,16 +813,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C15" s="4">
-        <v>754</v>
+        <v>851</v>
       </c>
       <c r="D15" s="9">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E15" s="13">
-        <v>2.5454545454545454</v>
+        <v>1.6428571428571428</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -832,16 +832,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="C16" s="4">
-        <v>549</v>
+        <v>651</v>
       </c>
       <c r="D16" s="9">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E16" s="13">
-        <v>2.2727272727272729</v>
+        <v>2.0714285714285716</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -851,16 +851,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>245</v>
+        <v>315</v>
       </c>
       <c r="C17" s="4">
-        <v>689</v>
+        <v>850</v>
       </c>
       <c r="D17" s="9">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E17" s="13">
-        <v>3.7272727272727271</v>
+        <v>3.0714285714285716</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -870,16 +870,16 @@
         <v>22</v>
       </c>
       <c r="B18" s="6">
-        <v>3830</v>
+        <v>4649</v>
       </c>
       <c r="C18" s="6">
-        <v>9595</v>
+        <v>11185</v>
       </c>
       <c r="D18" s="10">
-        <v>645</v>
+        <v>679</v>
       </c>
       <c r="E18" s="14">
-        <v>3.6647727272727271</v>
+        <v>3.03125</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -1105,13 +1105,21 @@
       <c r="L2" s="4">
         <v>0</v>
       </c>
-      <c r="M2" s="4"/>
+      <c r="M2" s="4">
+        <v>103</v>
+      </c>
       <c r="N2" s="4">
-        <v>103</v>
-      </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>75</v>
+      </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
@@ -1128,7 +1136,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>809</v>
+        <v>933</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1166,13 +1174,21 @@
       <c r="L3" s="4">
         <v>83</v>
       </c>
-      <c r="M3" s="4"/>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
       <c r="N3" s="4">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
+        <v>64</v>
+      </c>
+      <c r="O3" s="4">
+        <v>80</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -1189,7 +1205,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>732</v>
+        <v>876</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1227,13 +1243,21 @@
       <c r="L4" s="4">
         <v>0</v>
       </c>
-      <c r="M4" s="4"/>
+      <c r="M4" s="4">
+        <v>120</v>
+      </c>
       <c r="N4" s="4">
-        <v>120</v>
-      </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>90</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>90</v>
+      </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
@@ -1250,7 +1274,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>1027</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1288,13 +1312,21 @@
       <c r="L5" s="4">
         <v>100</v>
       </c>
-      <c r="M5" s="4"/>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
       <c r="N5" s="4">
         <v>0</v>
       </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>58</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>58</v>
+      </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
@@ -1311,7 +1343,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>790</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1349,13 +1381,21 @@
       <c r="L6" s="4">
         <v>105</v>
       </c>
-      <c r="M6" s="4"/>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
       <c r="N6" s="4">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="O6" s="4">
+        <v>65</v>
+      </c>
+      <c r="P6" s="4">
+        <v>87</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>87</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
@@ -1372,7 +1412,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>705</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1410,13 +1450,21 @@
       <c r="L7" s="4">
         <v>95</v>
       </c>
-      <c r="M7" s="4"/>
+      <c r="M7" s="4">
+        <v>118</v>
+      </c>
       <c r="N7" s="4">
-        <v>118</v>
-      </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="O7" s="4">
+        <v>84</v>
+      </c>
+      <c r="P7" s="4">
+        <v>69</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>69</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
@@ -1433,7 +1481,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>948</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1471,13 +1519,21 @@
       <c r="L8" s="4">
         <v>0</v>
       </c>
-      <c r="M8" s="4"/>
+      <c r="M8" s="4">
+        <v>95</v>
+      </c>
       <c r="N8" s="4">
-        <v>95</v>
-      </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>89</v>
+      </c>
+      <c r="P8" s="4">
+        <v>64</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>64</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
@@ -1494,7 +1550,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>899</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1532,13 +1588,21 @@
       <c r="L9" s="4">
         <v>88</v>
       </c>
-      <c r="M9" s="4"/>
+      <c r="M9" s="4">
+        <v>106</v>
+      </c>
       <c r="N9" s="4">
-        <v>106</v>
-      </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>83</v>
+      </c>
+      <c r="P9" s="4">
+        <v>84</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>84</v>
+      </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
@@ -1555,7 +1619,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>984</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1593,13 +1657,21 @@
       <c r="L10" s="4">
         <v>105</v>
       </c>
-      <c r="M10" s="4"/>
+      <c r="M10" s="4">
+        <v>103</v>
+      </c>
       <c r="N10" s="4">
-        <v>103</v>
-      </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+        <v>81</v>
+      </c>
+      <c r="O10" s="4">
+        <v>60</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0</v>
+      </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
@@ -1616,7 +1688,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>845</v>
+        <v>986</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1654,13 +1726,21 @@
       <c r="L11" s="4">
         <v>0</v>
       </c>
-      <c r="M11" s="4"/>
+      <c r="M11" s="4">
+        <v>101</v>
+      </c>
       <c r="N11" s="4">
-        <v>101</v>
-      </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="O11" s="4">
+        <v>43</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0</v>
+      </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -1677,7 +1757,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>720</v>
+        <v>808</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1715,13 +1795,21 @@
       <c r="L12" s="4">
         <v>0</v>
       </c>
-      <c r="M12" s="4"/>
+      <c r="M12" s="4">
+        <v>25</v>
+      </c>
       <c r="N12" s="4">
-        <v>25</v>
-      </c>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="O12" s="4">
+        <v>75</v>
+      </c>
+      <c r="P12" s="4">
+        <v>75</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>75</v>
+      </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
@@ -1738,7 +1826,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>820</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1776,13 +1864,21 @@
       <c r="L13" s="4">
         <v>67</v>
       </c>
-      <c r="M13" s="4"/>
+      <c r="M13" s="4">
+        <v>133</v>
+      </c>
       <c r="N13" s="4">
-        <v>133</v>
-      </c>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>7</v>
+      </c>
+      <c r="P13" s="4">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>54</v>
+      </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
@@ -1799,7 +1895,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>871</v>
+        <v>932</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1837,13 +1933,21 @@
       <c r="L14" s="4">
         <v>0</v>
       </c>
-      <c r="M14" s="4"/>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
       <c r="N14" s="4">
         <v>0</v>
       </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
+      <c r="O14" s="4">
+        <v>63</v>
+      </c>
+      <c r="P14" s="4">
+        <v>54</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>54</v>
+      </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
@@ -1860,7 +1964,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>709</v>
+        <v>826</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -1898,13 +2002,21 @@
       <c r="L15" s="4">
         <v>96</v>
       </c>
-      <c r="M15" s="4"/>
+      <c r="M15" s="4">
+        <v>105</v>
+      </c>
       <c r="N15" s="4">
-        <v>105</v>
-      </c>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4">
+        <v>44</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>44</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
@@ -1921,7 +2033,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>939</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -1959,13 +2071,21 @@
       <c r="L16" s="4">
         <v>84</v>
       </c>
-      <c r="M16" s="4"/>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
       <c r="N16" s="4">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
+        <v>51</v>
+      </c>
+      <c r="O16" s="4">
+        <v>59</v>
+      </c>
+      <c r="P16" s="4">
+        <v>35</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>35</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
@@ -1982,7 +2102,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>693</v>
+        <v>838</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2020,13 +2140,21 @@
       <c r="L17" s="4">
         <v>0</v>
       </c>
-      <c r="M17" s="4"/>
+      <c r="M17" s="4">
+        <v>118</v>
+      </c>
       <c r="N17" s="4">
-        <v>118</v>
-      </c>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="O17" s="4">
+        <v>85</v>
+      </c>
+      <c r="P17" s="4">
+        <v>71</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>71</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
@@ -2043,7 +2171,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>934</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2081,13 +2209,21 @@
       <c r="L18" s="6">
         <v>823</v>
       </c>
-      <c r="M18" s="6"/>
+      <c r="M18" s="6">
+        <v>1127</v>
+      </c>
       <c r="N18" s="6">
-        <v>1127</v>
-      </c>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
+        <v>756</v>
+      </c>
+      <c r="O18" s="6">
+        <v>793</v>
+      </c>
+      <c r="P18" s="6">
+        <v>860</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>860</v>
+      </c>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
       <c r="T18" s="6"/>
@@ -2104,7 +2240,7 @@
       <c r="AE18" s="6"/>
       <c r="AF18" s="6"/>
       <c r="AG18" s="10">
-        <v>13425</v>
+        <v>15834</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2177,7 +2313,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.6647727272727271</v>
+        <v>3.03125</v>
       </c>
     </row>
   </sheetData>

--- a/Juli-2026.xlsx
+++ b/Juli-2026.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F0707B-C049-430D-996E-E04C6D784849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68DC4CF-0829-4638-BCE7-A01EC13A6A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Trend" sheetId="2" r:id="rId2"/>
     <sheet name="Summary" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -591,10 +591,10 @@
         <v>584</v>
       </c>
       <c r="D3" s="9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E3" s="13">
-        <v>3.1428571428571428</v>
+        <v>3.2857142857142856</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -610,10 +610,10 @@
         <v>860</v>
       </c>
       <c r="D4" s="9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="13">
-        <v>2.9285714285714284</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -629,10 +629,10 @@
         <v>567</v>
       </c>
       <c r="D5" s="9">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E5" s="13">
-        <v>3.2142857142857144</v>
+        <v>3.5</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -648,10 +648,10 @@
         <v>630</v>
       </c>
       <c r="D6" s="9">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E6" s="13">
-        <v>3.3571428571428572</v>
+        <v>3.5714285714285716</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -667,10 +667,10 @@
         <v>749</v>
       </c>
       <c r="D7" s="9">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7" s="13">
-        <v>5.1428571428571432</v>
+        <v>5.2857142857142856</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -686,10 +686,10 @@
         <v>724</v>
       </c>
       <c r="D8" s="9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" s="13">
-        <v>4.4285714285714288</v>
+        <v>4.5714285714285712</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -705,10 +705,10 @@
         <v>855</v>
       </c>
       <c r="D9" s="9">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" s="13">
-        <v>3.5</v>
+        <v>3.5714285714285716</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -724,10 +724,10 @@
         <v>652</v>
       </c>
       <c r="D10" s="9">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E10" s="13">
-        <v>3.0714285714285716</v>
+        <v>3.2857142857142856</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -743,10 +743,10 @@
         <v>606</v>
       </c>
       <c r="D11" s="9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11" s="13">
-        <v>2.5714285714285716</v>
+        <v>2.6428571428571428</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -762,10 +762,10 @@
         <v>666</v>
       </c>
       <c r="D12" s="9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12" s="13">
-        <v>2.9285714285714284</v>
+        <v>3</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -781,10 +781,10 @@
         <v>677</v>
       </c>
       <c r="D13" s="9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E13" s="13">
-        <v>2.2857142857142856</v>
+        <v>2.4285714285714284</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -800,10 +800,10 @@
         <v>642</v>
       </c>
       <c r="D14" s="9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" s="13">
-        <v>1.6428571428571428</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -819,10 +819,10 @@
         <v>851</v>
       </c>
       <c r="D15" s="9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E15" s="13">
-        <v>1.6428571428571428</v>
+        <v>1.7857142857142858</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -857,10 +857,10 @@
         <v>850</v>
       </c>
       <c r="D17" s="9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E17" s="13">
-        <v>3.0714285714285716</v>
+        <v>3.1428571428571428</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -876,10 +876,10 @@
         <v>11185</v>
       </c>
       <c r="D18" s="10">
-        <v>679</v>
+        <v>705</v>
       </c>
       <c r="E18" s="14">
-        <v>3.03125</v>
+        <v>3.1473214285714284</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -2313,7 +2313,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.03125</v>
+        <v>3.1473214285714284</v>
       </c>
     </row>
   </sheetData>

--- a/Juli-2026.xlsx
+++ b/Juli-2026.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68DC4CF-0829-4638-BCE7-A01EC13A6A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921613AB-16D6-4782-85C9-AF55F547CBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Trend" sheetId="2" r:id="rId2"/>
     <sheet name="Summary" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -566,16 +566,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>312</v>
+        <v>443</v>
       </c>
       <c r="C2" s="4">
-        <v>621</v>
+        <v>924</v>
       </c>
       <c r="D2" s="9">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="E2" s="13">
-        <v>3.5</v>
+        <v>3.5263157894736841</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -585,16 +585,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>292</v>
+        <v>384</v>
       </c>
       <c r="C3" s="4">
-        <v>584</v>
+        <v>836</v>
       </c>
       <c r="D3" s="9">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E3" s="13">
-        <v>3.2857142857142856</v>
+        <v>2.8947368421052633</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -604,16 +604,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>348</v>
+        <v>485</v>
       </c>
       <c r="C4" s="4">
-        <v>860</v>
+        <v>1273</v>
       </c>
       <c r="D4" s="9">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E4" s="13">
-        <v>3</v>
+        <v>3.0526315789473686</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>281</v>
+        <v>393</v>
       </c>
       <c r="C5" s="4">
-        <v>567</v>
+        <v>792</v>
       </c>
       <c r="D5" s="9">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E5" s="13">
-        <v>3.5</v>
+        <v>3.6315789473684212</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -642,16 +642,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>301</v>
+        <v>448</v>
       </c>
       <c r="C6" s="4">
-        <v>630</v>
+        <v>1066</v>
       </c>
       <c r="D6" s="9">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E6" s="13">
-        <v>3.5714285714285716</v>
+        <v>3.4210526315789473</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -661,16 +661,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>422</v>
+        <v>542</v>
       </c>
       <c r="C7" s="4">
-        <v>749</v>
+        <v>988</v>
       </c>
       <c r="D7" s="9">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E7" s="13">
-        <v>5.2857142857142856</v>
+        <v>5.4210526315789478</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -680,16 +680,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>328</v>
+        <v>438</v>
       </c>
       <c r="C8" s="4">
-        <v>724</v>
+        <v>1050</v>
       </c>
       <c r="D8" s="9">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E8" s="13">
-        <v>4.5714285714285712</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -699,16 +699,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>296</v>
+        <v>383</v>
       </c>
       <c r="C9" s="4">
-        <v>855</v>
+        <v>1184</v>
       </c>
       <c r="D9" s="9">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E9" s="13">
-        <v>3.5714285714285716</v>
+        <v>3.7894736842105261</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -718,16 +718,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>334</v>
+        <v>456</v>
       </c>
       <c r="C10" s="4">
-        <v>652</v>
+        <v>869</v>
       </c>
       <c r="D10" s="9">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E10" s="13">
-        <v>3.2857142857142856</v>
+        <v>3.2105263157894739</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -737,16 +737,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="C11" s="4">
-        <v>606</v>
+        <v>1011</v>
       </c>
       <c r="D11" s="9">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E11" s="13">
-        <v>2.6428571428571428</v>
+        <v>2.9473684210526314</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -756,16 +756,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>380</v>
+        <v>486</v>
       </c>
       <c r="C12" s="4">
-        <v>666</v>
+        <v>909</v>
       </c>
       <c r="D12" s="9">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E12" s="13">
-        <v>3</v>
+        <v>3.1578947368421053</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -775,16 +775,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>255</v>
+        <v>343</v>
       </c>
       <c r="C13" s="4">
-        <v>677</v>
+        <v>907</v>
       </c>
       <c r="D13" s="9">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E13" s="13">
-        <v>2.4285714285714284</v>
+        <v>2.4736842105263159</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -794,16 +794,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>184</v>
+        <v>251</v>
       </c>
       <c r="C14" s="4">
-        <v>642</v>
+        <v>900</v>
       </c>
       <c r="D14" s="9">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E14" s="13">
-        <v>1.7142857142857142</v>
+        <v>1.6842105263157894</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -813,16 +813,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>212</v>
+        <v>286</v>
       </c>
       <c r="C15" s="4">
-        <v>851</v>
+        <v>1205</v>
       </c>
       <c r="D15" s="9">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E15" s="13">
-        <v>1.7857142857142858</v>
+        <v>1.5263157894736843</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -832,16 +832,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="C16" s="4">
-        <v>651</v>
+        <v>928</v>
       </c>
       <c r="D16" s="9">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E16" s="13">
-        <v>2.0714285714285716</v>
+        <v>2.2105263157894739</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -851,16 +851,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>315</v>
+        <v>395</v>
       </c>
       <c r="C17" s="4">
-        <v>850</v>
+        <v>1095</v>
       </c>
       <c r="D17" s="9">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E17" s="13">
-        <v>3.1428571428571428</v>
+        <v>3.1578947368421053</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -870,16 +870,16 @@
         <v>22</v>
       </c>
       <c r="B18" s="6">
-        <v>4649</v>
+        <v>6260</v>
       </c>
       <c r="C18" s="6">
-        <v>11185</v>
+        <v>15937</v>
       </c>
       <c r="D18" s="10">
-        <v>705</v>
+        <v>952</v>
       </c>
       <c r="E18" s="14">
-        <v>3.1473214285714284</v>
+        <v>3.1315789473684212</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -1120,11 +1120,21 @@
       <c r="Q2" s="4">
         <v>75</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>105</v>
+      </c>
+      <c r="T2" s="4">
+        <v>112</v>
+      </c>
+      <c r="U2" s="4">
+        <v>106</v>
+      </c>
+      <c r="V2" s="4">
+        <v>111</v>
+      </c>
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
@@ -1136,7 +1146,7 @@
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>933</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1189,11 +1199,21 @@
       <c r="Q3" s="4">
         <v>0</v>
       </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>119</v>
+      </c>
+      <c r="T3" s="4">
+        <v>114</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>111</v>
+      </c>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
@@ -1205,7 +1225,7 @@
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>876</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1258,11 +1278,21 @@
       <c r="Q4" s="4">
         <v>90</v>
       </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
+      <c r="R4" s="4">
+        <v>110</v>
+      </c>
+      <c r="S4" s="4">
+        <v>119</v>
+      </c>
+      <c r="T4" s="4">
+        <v>107</v>
+      </c>
+      <c r="U4" s="4">
+        <v>109</v>
+      </c>
+      <c r="V4" s="4">
+        <v>105</v>
+      </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -1274,7 +1304,7 @@
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>1208</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1327,11 +1357,21 @@
       <c r="Q5" s="4">
         <v>58</v>
       </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
+        <v>118</v>
+      </c>
+      <c r="T5" s="4">
+        <v>109</v>
+      </c>
+      <c r="U5" s="4">
+        <v>110</v>
+      </c>
+      <c r="V5" s="4">
+        <v>0</v>
+      </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
@@ -1343,7 +1383,7 @@
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>848</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1396,11 +1436,21 @@
       <c r="Q6" s="4">
         <v>87</v>
       </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
+      <c r="R6" s="4">
+        <v>121</v>
+      </c>
+      <c r="S6" s="4">
+        <v>120</v>
+      </c>
+      <c r="T6" s="4">
+        <v>112</v>
+      </c>
+      <c r="U6" s="4">
+        <v>120</v>
+      </c>
+      <c r="V6" s="4">
+        <v>110</v>
+      </c>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
@@ -1412,7 +1462,7 @@
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>931</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1465,11 +1515,21 @@
       <c r="Q7" s="4">
         <v>69</v>
       </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
+      <c r="R7" s="4">
+        <v>114</v>
+      </c>
+      <c r="S7" s="4">
+        <v>1</v>
+      </c>
+      <c r="T7" s="4">
+        <v>124</v>
+      </c>
+      <c r="U7" s="4">
+        <v>120</v>
+      </c>
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
@@ -1481,7 +1541,7 @@
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>1171</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1534,11 +1594,21 @@
       <c r="Q8" s="4">
         <v>64</v>
       </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
+        <v>110</v>
+      </c>
+      <c r="T8" s="4">
+        <v>108</v>
+      </c>
+      <c r="U8" s="4">
+        <v>114</v>
+      </c>
+      <c r="V8" s="4">
+        <v>104</v>
+      </c>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
@@ -1550,7 +1620,7 @@
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>1052</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1603,11 +1673,21 @@
       <c r="Q9" s="4">
         <v>84</v>
       </c>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
+      <c r="R9" s="4">
+        <v>93</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4">
+        <v>111</v>
+      </c>
+      <c r="U9" s="4">
+        <v>110</v>
+      </c>
+      <c r="V9" s="4">
+        <v>102</v>
+      </c>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
@@ -1619,7 +1699,7 @@
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>1151</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1672,11 +1752,21 @@
       <c r="Q10" s="4">
         <v>0</v>
       </c>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
+      <c r="R10" s="4">
+        <v>119</v>
+      </c>
+      <c r="S10" s="4">
+        <v>110</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4">
+        <v>110</v>
+      </c>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
@@ -1688,7 +1778,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>986</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1741,11 +1831,21 @@
       <c r="Q11" s="4">
         <v>0</v>
       </c>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
+      <c r="R11" s="4">
+        <v>62</v>
+      </c>
+      <c r="S11" s="4">
+        <v>104</v>
+      </c>
+      <c r="T11" s="4">
+        <v>110</v>
+      </c>
+      <c r="U11" s="4">
+        <v>108</v>
+      </c>
+      <c r="V11" s="4">
+        <v>109</v>
+      </c>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
@@ -1757,7 +1857,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>808</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1810,11 +1910,21 @@
       <c r="Q12" s="4">
         <v>75</v>
       </c>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
+      <c r="R12" s="4">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4">
+        <v>118</v>
+      </c>
+      <c r="T12" s="4">
+        <v>115</v>
+      </c>
+      <c r="U12" s="4">
+        <v>116</v>
+      </c>
+      <c r="V12" s="4">
+        <v>0</v>
+      </c>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -1826,7 +1936,7 @@
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>1046</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1879,11 +1989,21 @@
       <c r="Q13" s="4">
         <v>54</v>
       </c>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
+      <c r="R13" s="4">
+        <v>108</v>
+      </c>
+      <c r="S13" s="4">
+        <v>103</v>
+      </c>
+      <c r="T13" s="4">
+        <v>107</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
+        <v>0</v>
+      </c>
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
@@ -1895,7 +2015,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>932</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1948,11 +2068,21 @@
       <c r="Q14" s="4">
         <v>54</v>
       </c>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
+        <v>101</v>
+      </c>
+      <c r="U14" s="4">
+        <v>115</v>
+      </c>
+      <c r="V14" s="4">
+        <v>109</v>
+      </c>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
@@ -1964,7 +2094,7 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>826</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2017,11 +2147,21 @@
       <c r="Q15" s="4">
         <v>44</v>
       </c>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4">
+        <v>103</v>
+      </c>
+      <c r="T15" s="4">
+        <v>109</v>
+      </c>
+      <c r="U15" s="4">
+        <v>113</v>
+      </c>
+      <c r="V15" s="4">
+        <v>103</v>
+      </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
@@ -2033,7 +2173,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>1063</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2086,11 +2226,21 @@
       <c r="Q16" s="4">
         <v>35</v>
       </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>109</v>
+      </c>
+      <c r="U16" s="4">
+        <v>108</v>
+      </c>
+      <c r="V16" s="4">
+        <v>110</v>
+      </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2102,7 +2252,7 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>838</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2155,11 +2305,21 @@
       <c r="Q17" s="4">
         <v>71</v>
       </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4">
+        <v>109</v>
+      </c>
+      <c r="U17" s="4">
+        <v>109</v>
+      </c>
+      <c r="V17" s="4">
+        <v>107</v>
+      </c>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
@@ -2171,7 +2331,7 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>1165</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2224,11 +2384,21 @@
       <c r="Q18" s="6">
         <v>860</v>
       </c>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
+      <c r="R18" s="6">
+        <v>727</v>
+      </c>
+      <c r="S18" s="6">
+        <v>1230</v>
+      </c>
+      <c r="T18" s="6">
+        <v>1657</v>
+      </c>
+      <c r="U18" s="6">
+        <v>1458</v>
+      </c>
+      <c r="V18" s="6">
+        <v>1291</v>
+      </c>
       <c r="W18" s="6"/>
       <c r="X18" s="6"/>
       <c r="Y18" s="6"/>
@@ -2240,7 +2410,7 @@
       <c r="AE18" s="6"/>
       <c r="AF18" s="6"/>
       <c r="AG18" s="10">
-        <v>15834</v>
+        <v>22197</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2313,7 +2483,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.1473214285714284</v>
+        <v>3.1315789473684212</v>
       </c>
     </row>
   </sheetData>

--- a/Juli-2026.xlsx
+++ b/Juli-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921613AB-16D6-4782-85C9-AF55F547CBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CB7A08-A810-4AA1-9C80-15F8C6B9E29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,16 +566,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>443</v>
+        <v>282</v>
       </c>
       <c r="C2" s="4">
-        <v>924</v>
+        <v>566</v>
       </c>
       <c r="D2" s="9">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E2" s="13">
-        <v>3.5263157894736841</v>
+        <v>3.1739130434782608</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -585,16 +585,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>384</v>
+        <v>284</v>
       </c>
       <c r="C3" s="4">
-        <v>836</v>
+        <v>613</v>
       </c>
       <c r="D3" s="9">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E3" s="13">
-        <v>2.8947368421052633</v>
+        <v>2.8260869565217392</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -604,16 +604,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>485</v>
+        <v>265</v>
       </c>
       <c r="C4" s="4">
-        <v>1273</v>
+        <v>570</v>
       </c>
       <c r="D4" s="9">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E4" s="13">
-        <v>3.0526315789473686</v>
+        <v>2.8695652173913042</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>393</v>
+        <v>300</v>
       </c>
       <c r="C5" s="4">
-        <v>792</v>
+        <v>598</v>
       </c>
       <c r="D5" s="9">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="E5" s="13">
-        <v>3.6315789473684212</v>
+        <v>3.8260869565217392</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -642,16 +642,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>448</v>
+        <v>300</v>
       </c>
       <c r="C6" s="4">
-        <v>1066</v>
+        <v>586</v>
       </c>
       <c r="D6" s="9">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E6" s="13">
-        <v>3.4210526315789473</v>
+        <v>3.2173913043478262</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -661,16 +661,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>542</v>
+        <v>372</v>
       </c>
       <c r="C7" s="4">
-        <v>988</v>
+        <v>662</v>
       </c>
       <c r="D7" s="9">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E7" s="13">
-        <v>5.4210526315789478</v>
+        <v>4.7826086956521738</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -680,16 +680,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>438</v>
+        <v>316</v>
       </c>
       <c r="C8" s="4">
-        <v>1050</v>
+        <v>631</v>
       </c>
       <c r="D8" s="9">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E8" s="13">
-        <v>4</v>
+        <v>3.7826086956521738</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -699,16 +699,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>383</v>
+        <v>300</v>
       </c>
       <c r="C9" s="4">
-        <v>1184</v>
+        <v>619</v>
       </c>
       <c r="D9" s="9">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E9" s="13">
-        <v>3.7894736842105261</v>
+        <v>3.3913043478260869</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -718,16 +718,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>456</v>
+        <v>337</v>
       </c>
       <c r="C10" s="4">
-        <v>869</v>
+        <v>463</v>
       </c>
       <c r="D10" s="9">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E10" s="13">
-        <v>3.2105263157894739</v>
+        <v>3.5652173913043477</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -737,16 +737,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>290</v>
+        <v>199</v>
       </c>
       <c r="C11" s="4">
-        <v>1011</v>
+        <v>622</v>
       </c>
       <c r="D11" s="9">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E11" s="13">
-        <v>2.9473684210526314</v>
+        <v>2.6086956521739131</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -756,16 +756,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>486</v>
+        <v>337</v>
       </c>
       <c r="C12" s="4">
-        <v>909</v>
+        <v>596</v>
       </c>
       <c r="D12" s="9">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E12" s="13">
-        <v>3.1578947368421053</v>
+        <v>2.7391304347826089</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -775,16 +775,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>343</v>
+        <v>248</v>
       </c>
       <c r="C13" s="4">
-        <v>907</v>
+        <v>707</v>
       </c>
       <c r="D13" s="9">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E13" s="13">
-        <v>2.4736842105263159</v>
+        <v>2.3043478260869565</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -794,16 +794,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>251</v>
+        <v>162</v>
       </c>
       <c r="C14" s="4">
-        <v>900</v>
+        <v>659</v>
       </c>
       <c r="D14" s="9">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E14" s="13">
-        <v>1.6842105263157894</v>
+        <v>1.9565217391304348</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -813,16 +813,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>286</v>
+        <v>187</v>
       </c>
       <c r="C15" s="4">
-        <v>1205</v>
+        <v>667</v>
       </c>
       <c r="D15" s="9">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E15" s="13">
-        <v>1.5263157894736843</v>
+        <v>1.7391304347826086</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -832,16 +832,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>237</v>
+        <v>175</v>
       </c>
       <c r="C16" s="4">
-        <v>928</v>
+        <v>731</v>
       </c>
       <c r="D16" s="9">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E16" s="13">
-        <v>2.2105263157894739</v>
+        <v>2.0434782608695654</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -851,16 +851,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>395</v>
+        <v>273</v>
       </c>
       <c r="C17" s="4">
-        <v>1095</v>
+        <v>696</v>
       </c>
       <c r="D17" s="9">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E17" s="13">
-        <v>3.1578947368421053</v>
+        <v>3.2173913043478262</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -870,16 +870,16 @@
         <v>22</v>
       </c>
       <c r="B18" s="6">
-        <v>6260</v>
+        <v>4337</v>
       </c>
       <c r="C18" s="6">
-        <v>15937</v>
+        <v>9986</v>
       </c>
       <c r="D18" s="10">
-        <v>952</v>
+        <v>1105</v>
       </c>
       <c r="E18" s="14">
-        <v>3.1315789473684212</v>
+        <v>3.0027173913043477</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -1075,78 +1075,72 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>102</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="C2" s="4"/>
       <c r="D2" s="4">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E2" s="4">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="H2" s="4">
+        <v>99</v>
+      </c>
+      <c r="I2" s="4">
+        <v>89</v>
+      </c>
+      <c r="J2" s="4">
+        <v>84</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4">
+        <v>94</v>
+      </c>
+      <c r="O2" s="4">
+        <v>99</v>
+      </c>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4">
+        <v>97</v>
+      </c>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4">
+        <v>99</v>
+      </c>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4">
         <v>104</v>
       </c>
-      <c r="I2" s="4">
-        <v>96</v>
-      </c>
-      <c r="J2" s="4">
-        <v>89</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4">
-        <v>103</v>
-      </c>
-      <c r="N2" s="4">
-        <v>49</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>75</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>75</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
-        <v>105</v>
-      </c>
-      <c r="T2" s="4">
-        <v>112</v>
-      </c>
-      <c r="U2" s="4">
-        <v>106</v>
-      </c>
       <c r="V2" s="4">
-        <v>111</v>
-      </c>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="W2" s="4">
+        <v>108</v>
+      </c>
+      <c r="X2" s="4">
+        <v>101</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>102</v>
+      </c>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
+      <c r="AB2" s="4">
+        <v>93</v>
+      </c>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
       <c r="AF2" s="4"/>
       <c r="AG2" s="9">
-        <v>1367</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1154,78 +1148,72 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C3" s="4">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D3" s="4">
-        <v>61</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H3" s="4">
+        <v>90</v>
+      </c>
+      <c r="I3" s="4">
+        <v>78</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4">
+        <v>112</v>
+      </c>
+      <c r="L3" s="4">
+        <v>80</v>
+      </c>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4">
+        <v>106</v>
+      </c>
+      <c r="P3" s="4">
+        <v>103</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4">
+        <v>112</v>
+      </c>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4">
+        <v>107</v>
+      </c>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4">
+        <v>108</v>
+      </c>
+      <c r="X3" s="4">
+        <v>103</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>116</v>
+      </c>
+      <c r="Z3" s="4">
         <v>96</v>
       </c>
-      <c r="I3" s="4">
-        <v>84</v>
-      </c>
-      <c r="J3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4">
-        <v>120</v>
-      </c>
-      <c r="L3" s="4">
-        <v>83</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>64</v>
-      </c>
-      <c r="O3" s="4">
-        <v>80</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4">
-        <v>119</v>
-      </c>
-      <c r="T3" s="4">
-        <v>114</v>
-      </c>
-      <c r="U3" s="4">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4">
-        <v>111</v>
-      </c>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
+      <c r="AB3" s="4">
+        <v>90</v>
+      </c>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>1220</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1233,78 +1221,76 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>144</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E4" s="4">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H4" s="4">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="I4" s="4">
+        <v>104</v>
+      </c>
+      <c r="J4" s="4">
+        <v>105</v>
+      </c>
+      <c r="K4" s="4">
         <v>111</v>
       </c>
-      <c r="J4" s="4">
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4">
+        <v>110</v>
+      </c>
+      <c r="O4" s="4">
+        <v>104</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4">
+        <v>100</v>
+      </c>
+      <c r="R4" s="4">
+        <v>101</v>
+      </c>
+      <c r="S4" s="4">
         <v>112</v>
       </c>
-      <c r="K4" s="4">
-        <v>115</v>
-      </c>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>120</v>
-      </c>
-      <c r="N4" s="4">
-        <v>91</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <v>90</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>90</v>
-      </c>
-      <c r="R4" s="4">
-        <v>110</v>
-      </c>
-      <c r="S4" s="4">
-        <v>119</v>
-      </c>
-      <c r="T4" s="4">
-        <v>107</v>
-      </c>
+      <c r="T4" s="4"/>
       <c r="U4" s="4">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="V4" s="4">
-        <v>105</v>
-      </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
+        <v>102</v>
+      </c>
+      <c r="W4" s="4">
+        <v>100</v>
+      </c>
+      <c r="X4" s="4">
+        <v>99</v>
+      </c>
       <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
+      <c r="Z4" s="4">
+        <v>108</v>
+      </c>
       <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
+      <c r="AB4" s="4">
+        <v>13</v>
+      </c>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="9">
-        <v>1758</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1312,78 +1298,70 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4">
+        <v>101</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4">
+        <v>100</v>
+      </c>
+      <c r="I5" s="4">
+        <v>98</v>
+      </c>
+      <c r="J5" s="4">
+        <v>101</v>
+      </c>
+      <c r="K5" s="4">
+        <v>114</v>
+      </c>
+      <c r="L5" s="4">
+        <v>98</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4">
+        <v>93</v>
+      </c>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4">
+        <v>115</v>
+      </c>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4">
         <v>105</v>
       </c>
-      <c r="D5" s="4">
-        <v>48</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="V5" s="4">
         <v>105</v>
       </c>
-      <c r="I5" s="4">
-        <v>102</v>
-      </c>
-      <c r="J5" s="4">
-        <v>105</v>
-      </c>
-      <c r="K5" s="4">
-        <v>118</v>
-      </c>
-      <c r="L5" s="4">
-        <v>100</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>58</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>58</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4">
-        <v>118</v>
-      </c>
-      <c r="T5" s="4">
+      <c r="W5" s="4"/>
+      <c r="X5" s="4">
+        <v>108</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>137</v>
+      </c>
+      <c r="Z5" s="4">
         <v>109</v>
       </c>
-      <c r="U5" s="4">
-        <v>110</v>
-      </c>
-      <c r="V5" s="4">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
+      <c r="AB5" s="4">
+        <v>97</v>
+      </c>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="9">
-        <v>1185</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1394,75 +1372,73 @@
         <v>1</v>
       </c>
       <c r="C6" s="4">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D6" s="4">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E6" s="4">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H6" s="4">
         <v>1</v>
       </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
+      <c r="I6" s="4"/>
       <c r="J6" s="4">
+        <v>91</v>
+      </c>
+      <c r="K6" s="4">
+        <v>56</v>
+      </c>
+      <c r="L6" s="4">
         <v>98</v>
       </c>
-      <c r="K6" s="4">
-        <v>64</v>
-      </c>
-      <c r="L6" s="4">
-        <v>105</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4">
-        <v>74</v>
-      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
       <c r="O6" s="4">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="P6" s="4">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="Q6" s="4">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="R6" s="4">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="S6" s="4">
-        <v>120</v>
-      </c>
-      <c r="T6" s="4">
-        <v>112</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="T6" s="4"/>
       <c r="U6" s="4">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="V6" s="4">
-        <v>110</v>
-      </c>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
+        <v>117</v>
+      </c>
+      <c r="W6" s="4">
+        <v>106</v>
+      </c>
+      <c r="X6" s="4">
+        <v>100</v>
+      </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
+      <c r="AB6" s="4">
+        <v>108</v>
+      </c>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="9">
-        <v>1514</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1470,78 +1446,76 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C7" s="4">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D7" s="4">
-        <v>63</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
-        <v>125</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="H7" s="4"/>
       <c r="I7" s="4">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J7" s="4">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="K7" s="4">
+        <v>104</v>
+      </c>
+      <c r="L7" s="4">
+        <v>87</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4">
         <v>111</v>
       </c>
-      <c r="L7" s="4">
-        <v>95</v>
-      </c>
-      <c r="M7" s="4">
-        <v>118</v>
-      </c>
-      <c r="N7" s="4">
-        <v>70</v>
-      </c>
       <c r="O7" s="4">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="P7" s="4">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="Q7" s="4">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="R7" s="4">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="S7" s="4">
         <v>1</v>
       </c>
-      <c r="T7" s="4">
-        <v>124</v>
-      </c>
+      <c r="T7" s="4"/>
       <c r="U7" s="4">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="V7" s="4">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
+      <c r="X7" s="4">
+        <v>109</v>
+      </c>
       <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
+      <c r="Z7" s="4">
+        <v>103</v>
+      </c>
       <c r="AA7" s="4"/>
-      <c r="AB7" s="4"/>
+      <c r="AB7" s="4">
+        <v>103</v>
+      </c>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="9">
-        <v>1530</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1549,78 +1523,72 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
+        <v>103</v>
+      </c>
+      <c r="C8" s="4">
+        <v>100</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4">
+        <v>117</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4">
+        <v>131</v>
+      </c>
+      <c r="I8" s="4">
         <v>108</v>
       </c>
-      <c r="C8" s="4">
-        <v>104</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
-        <v>125</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="J8" s="4">
+        <v>106</v>
+      </c>
+      <c r="K8" s="4">
+        <v>100</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4">
+        <v>90</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4">
+        <v>98</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>109</v>
+      </c>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4">
+        <v>101</v>
+      </c>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4">
+        <v>99</v>
+      </c>
+      <c r="V8" s="4">
+        <v>110</v>
+      </c>
+      <c r="W8" s="4">
+        <v>102</v>
+      </c>
+      <c r="X8" s="4">
+        <v>105</v>
+      </c>
+      <c r="Y8" s="4">
         <v>138</v>
       </c>
-      <c r="I8" s="4">
-        <v>114</v>
-      </c>
-      <c r="J8" s="4">
-        <v>111</v>
-      </c>
-      <c r="K8" s="4">
-        <v>104</v>
-      </c>
-      <c r="L8" s="4">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
-        <v>95</v>
-      </c>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <v>89</v>
-      </c>
-      <c r="P8" s="4">
-        <v>64</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>64</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
-        <v>110</v>
-      </c>
-      <c r="T8" s="4">
-        <v>108</v>
-      </c>
-      <c r="U8" s="4">
-        <v>114</v>
-      </c>
-      <c r="V8" s="4">
-        <v>104</v>
-      </c>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
+      <c r="AB8" s="4">
+        <v>105</v>
+      </c>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="9">
-        <v>1488</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1628,78 +1596,72 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C9" s="4">
-        <v>128</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="4">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H9" s="4">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I9" s="4">
+        <v>100</v>
+      </c>
+      <c r="J9" s="4">
+        <v>86</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4">
+        <v>85</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4">
+        <v>102</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4">
         <v>103</v>
       </c>
-      <c r="J9" s="4">
+      <c r="Q9" s="4">
+        <v>106</v>
+      </c>
+      <c r="R9" s="4">
         <v>92</v>
       </c>
-      <c r="K9" s="4">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4">
-        <v>88</v>
-      </c>
-      <c r="M9" s="4">
-        <v>106</v>
-      </c>
-      <c r="N9" s="4">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4">
-        <v>83</v>
-      </c>
-      <c r="P9" s="4">
-        <v>84</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>84</v>
-      </c>
-      <c r="R9" s="4">
-        <v>93</v>
-      </c>
-      <c r="S9" s="4">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4">
-        <v>111</v>
-      </c>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
       <c r="U9" s="4">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V9" s="4">
         <v>102</v>
       </c>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
+      <c r="W9" s="4">
+        <v>101</v>
+      </c>
+      <c r="X9" s="4">
+        <v>96</v>
+      </c>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
-      <c r="AB9" s="4"/>
+      <c r="AB9" s="4">
+        <v>97</v>
+      </c>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="9">
-        <v>1567</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1707,70 +1669,60 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C10" s="4">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D10" s="4">
-        <v>67</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
+        <v>91</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4">
+        <v>103</v>
+      </c>
+      <c r="K10" s="4">
+        <v>103</v>
+      </c>
+      <c r="L10" s="4">
         <v>99</v>
       </c>
-      <c r="H10" s="4">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4">
-        <v>111</v>
-      </c>
-      <c r="K10" s="4">
+      <c r="M10" s="4"/>
+      <c r="N10" s="4">
+        <v>97</v>
+      </c>
+      <c r="O10" s="4">
+        <v>103</v>
+      </c>
+      <c r="P10" s="4">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4">
+        <v>115</v>
+      </c>
+      <c r="S10" s="4">
         <v>106</v>
       </c>
-      <c r="L10" s="4">
-        <v>105</v>
-      </c>
-      <c r="M10" s="4">
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4">
+        <v>106</v>
+      </c>
+      <c r="X10" s="4">
         <v>103</v>
       </c>
-      <c r="N10" s="4">
-        <v>81</v>
-      </c>
-      <c r="O10" s="4">
-        <v>60</v>
-      </c>
-      <c r="P10" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4">
-        <v>119</v>
-      </c>
-      <c r="S10" s="4">
-        <v>110</v>
-      </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4">
-        <v>110</v>
-      </c>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
+      <c r="Z10" s="4">
+        <v>102</v>
+      </c>
       <c r="AA10" s="4"/>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
@@ -1778,7 +1730,7 @@
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="9">
-        <v>1325</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1786,68 +1738,62 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>91</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C11" s="4"/>
       <c r="D11" s="4">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" s="4">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4">
+        <v>73</v>
+      </c>
+      <c r="H11" s="4">
+        <v>62</v>
+      </c>
+      <c r="I11" s="4">
+        <v>62</v>
+      </c>
+      <c r="J11" s="4">
+        <v>63</v>
+      </c>
+      <c r="K11" s="4">
         <v>78</v>
       </c>
-      <c r="H11" s="4">
-        <v>67</v>
-      </c>
-      <c r="I11" s="4">
-        <v>67</v>
-      </c>
-      <c r="J11" s="4">
-        <v>65</v>
-      </c>
-      <c r="K11" s="4">
-        <v>81</v>
-      </c>
-      <c r="L11" s="4">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <v>101</v>
-      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
       <c r="N11" s="4">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="O11" s="4">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="P11" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>0</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="Q11" s="4"/>
       <c r="R11" s="4">
         <v>62</v>
       </c>
       <c r="S11" s="4">
-        <v>104</v>
-      </c>
-      <c r="T11" s="4">
-        <v>110</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="T11" s="4"/>
       <c r="U11" s="4">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="V11" s="4">
+        <v>103</v>
+      </c>
+      <c r="W11" s="4">
         <v>109</v>
       </c>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
+      <c r="X11" s="4">
+        <v>5</v>
+      </c>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
@@ -1857,7 +1803,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="9">
-        <v>1301</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1865,78 +1811,72 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C12" s="4">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D12" s="4">
-        <v>100</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H12" s="4">
-        <v>113</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="I12" s="4"/>
       <c r="J12" s="4">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="K12" s="4">
-        <v>109</v>
-      </c>
-      <c r="L12" s="4">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4">
-        <v>25</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
       <c r="N12" s="4">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="O12" s="4">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="P12" s="4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="4">
-        <v>75</v>
-      </c>
-      <c r="R12" s="4">
-        <v>0</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="R12" s="4"/>
       <c r="S12" s="4">
-        <v>118</v>
-      </c>
-      <c r="T12" s="4">
-        <v>115</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="T12" s="4"/>
       <c r="U12" s="4">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="V12" s="4">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
+      <c r="X12" s="4">
+        <v>107</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>120</v>
+      </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
+      <c r="AB12" s="4">
+        <v>97</v>
+      </c>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="9">
-        <v>1395</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1944,78 +1884,72 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C13" s="4">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D13" s="4">
-        <v>75</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H13" s="4">
+        <v>89</v>
+      </c>
+      <c r="I13" s="4">
         <v>96</v>
       </c>
-      <c r="I13" s="4">
-        <v>100</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0</v>
-      </c>
+      <c r="J13" s="4"/>
       <c r="K13" s="4">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="L13" s="4">
-        <v>67</v>
-      </c>
-      <c r="M13" s="4">
-        <v>133</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="M13" s="4"/>
       <c r="N13" s="4">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4">
-        <v>7</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O13" s="4"/>
       <c r="P13" s="4">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="Q13" s="4">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="R13" s="4">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="S13" s="4">
+        <v>94</v>
+      </c>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4">
+        <v>101</v>
+      </c>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4">
         <v>103</v>
       </c>
-      <c r="T13" s="4">
-        <v>107</v>
-      </c>
-      <c r="U13" s="4">
-        <v>0</v>
-      </c>
-      <c r="V13" s="4">
-        <v>0</v>
-      </c>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
+      <c r="Z13" s="4">
+        <v>113</v>
+      </c>
       <c r="AA13" s="4"/>
-      <c r="AB13" s="4"/>
+      <c r="AB13" s="4">
+        <v>94</v>
+      </c>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>1250</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -2023,78 +1957,68 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C14" s="4">
+        <v>107</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4">
+        <v>97</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4">
+        <v>93</v>
+      </c>
+      <c r="I14" s="4">
+        <v>93</v>
+      </c>
+      <c r="J14" s="4">
+        <v>105</v>
+      </c>
+      <c r="K14" s="4">
+        <v>98</v>
+      </c>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4">
+        <v>103</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>99</v>
+      </c>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4">
+        <v>97</v>
+      </c>
+      <c r="V14" s="4">
         <v>112</v>
       </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>101</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>96</v>
-      </c>
-      <c r="I14" s="4">
-        <v>98</v>
-      </c>
-      <c r="J14" s="4">
+      <c r="W14" s="4">
+        <v>107</v>
+      </c>
+      <c r="X14" s="4">
+        <v>94</v>
+      </c>
+      <c r="Y14" s="4">
         <v>106</v>
       </c>
-      <c r="K14" s="4">
-        <v>104</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4">
-        <v>0</v>
-      </c>
-      <c r="O14" s="4">
-        <v>63</v>
-      </c>
-      <c r="P14" s="4">
-        <v>54</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>54</v>
-      </c>
-      <c r="R14" s="4">
-        <v>0</v>
-      </c>
-      <c r="S14" s="4">
-        <v>0</v>
-      </c>
-      <c r="T14" s="4">
-        <v>101</v>
-      </c>
-      <c r="U14" s="4">
-        <v>115</v>
-      </c>
-      <c r="V14" s="4">
-        <v>109</v>
-      </c>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
-      <c r="AB14" s="4"/>
+      <c r="AB14" s="4">
+        <v>102</v>
+      </c>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="9">
-        <v>1151</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2102,69 +2026,63 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C15" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D15" s="4">
-        <v>89</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
+        <v>101</v>
+      </c>
+      <c r="H15" s="4">
+        <v>108</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4">
+        <v>91</v>
+      </c>
+      <c r="K15" s="4">
+        <v>97</v>
+      </c>
+      <c r="L15" s="4">
+        <v>90</v>
+      </c>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4">
+        <v>99</v>
+      </c>
+      <c r="O15" s="4">
+        <v>103</v>
+      </c>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4">
+        <v>99</v>
+      </c>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4">
+        <v>99</v>
+      </c>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4">
+        <v>104</v>
+      </c>
+      <c r="V15" s="4">
         <v>106</v>
       </c>
-      <c r="H15" s="4">
-        <v>113</v>
-      </c>
-      <c r="I15" s="4">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4">
-        <v>96</v>
-      </c>
-      <c r="K15" s="4">
-        <v>101</v>
-      </c>
-      <c r="L15" s="4">
-        <v>96</v>
-      </c>
-      <c r="M15" s="4">
-        <v>105</v>
-      </c>
-      <c r="N15" s="4">
-        <v>80</v>
-      </c>
-      <c r="O15" s="4">
-        <v>0</v>
-      </c>
-      <c r="P15" s="4">
-        <v>44</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>44</v>
-      </c>
-      <c r="R15" s="4">
-        <v>0</v>
-      </c>
-      <c r="S15" s="4">
-        <v>103</v>
-      </c>
-      <c r="T15" s="4">
-        <v>109</v>
-      </c>
-      <c r="U15" s="4">
-        <v>113</v>
-      </c>
-      <c r="V15" s="4">
-        <v>103</v>
-      </c>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
+      <c r="W15" s="4">
+        <v>102</v>
+      </c>
+      <c r="X15" s="4">
+        <v>102</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>127</v>
+      </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
       <c r="AB15" s="4"/>
@@ -2173,7 +2091,7 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>1491</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2181,157 +2099,147 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="4">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D16" s="4">
-        <v>67</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
+        <v>110</v>
+      </c>
+      <c r="H16" s="4">
+        <v>99</v>
+      </c>
+      <c r="I16" s="4">
+        <v>76</v>
+      </c>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4">
+        <v>92</v>
+      </c>
+      <c r="L16" s="4">
+        <v>78</v>
+      </c>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4">
+        <v>50</v>
+      </c>
+      <c r="P16" s="4">
+        <v>107</v>
+      </c>
+      <c r="Q16" s="4">
         <v>111</v>
       </c>
-      <c r="H16" s="4">
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4">
+        <v>105</v>
+      </c>
+      <c r="V16" s="4">
         <v>104</v>
       </c>
-      <c r="I16" s="4">
-        <v>80</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4">
-        <v>95</v>
-      </c>
-      <c r="L16" s="4">
-        <v>84</v>
-      </c>
-      <c r="M16" s="4">
-        <v>0</v>
-      </c>
-      <c r="N16" s="4">
-        <v>51</v>
-      </c>
-      <c r="O16" s="4">
-        <v>59</v>
-      </c>
-      <c r="P16" s="4">
-        <v>35</v>
-      </c>
-      <c r="Q16" s="4">
-        <v>35</v>
-      </c>
-      <c r="R16" s="4">
-        <v>0</v>
-      </c>
-      <c r="S16" s="4">
-        <v>0</v>
-      </c>
-      <c r="T16" s="4">
-        <v>109</v>
-      </c>
-      <c r="U16" s="4">
-        <v>108</v>
-      </c>
-      <c r="V16" s="4">
+      <c r="W16" s="4">
+        <v>106</v>
+      </c>
+      <c r="X16" s="4">
+        <v>106</v>
+      </c>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4">
+        <v>112</v>
+      </c>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="4">
         <v>110</v>
       </c>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
-      <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="9">
-        <v>1165</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="4">
-        <v>0</v>
-      </c>
+      <c r="B17" s="4"/>
       <c r="C17" s="4">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D17" s="4">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E17" s="4">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4">
+        <v>101</v>
+      </c>
+      <c r="H17" s="4">
+        <v>93</v>
+      </c>
+      <c r="I17" s="4">
+        <v>95</v>
+      </c>
+      <c r="J17" s="4">
+        <v>98</v>
+      </c>
+      <c r="K17" s="4">
+        <v>102</v>
+      </c>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4">
+        <v>111</v>
+      </c>
+      <c r="O17" s="4">
+        <v>98</v>
+      </c>
+      <c r="P17" s="4">
+        <v>111</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>100</v>
+      </c>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4">
         <v>106</v>
       </c>
-      <c r="H17" s="4">
-        <v>98</v>
-      </c>
-      <c r="I17" s="4">
-        <v>99</v>
-      </c>
-      <c r="J17" s="4">
+      <c r="V17" s="4">
+        <v>104</v>
+      </c>
+      <c r="W17" s="4">
         <v>103</v>
       </c>
-      <c r="K17" s="4">
-        <v>106</v>
-      </c>
-      <c r="L17" s="4">
-        <v>0</v>
-      </c>
-      <c r="M17" s="4">
-        <v>118</v>
-      </c>
-      <c r="N17" s="4">
-        <v>75</v>
-      </c>
-      <c r="O17" s="4">
-        <v>85</v>
-      </c>
-      <c r="P17" s="4">
-        <v>71</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>71</v>
-      </c>
-      <c r="R17" s="4">
-        <v>0</v>
-      </c>
-      <c r="S17" s="4">
-        <v>0</v>
-      </c>
-      <c r="T17" s="4">
-        <v>109</v>
-      </c>
-      <c r="U17" s="4">
-        <v>109</v>
-      </c>
-      <c r="V17" s="4">
-        <v>107</v>
-      </c>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+      <c r="X17" s="4">
+        <v>100</v>
+      </c>
       <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
+      <c r="Z17" s="4">
+        <v>105</v>
+      </c>
       <c r="AA17" s="4"/>
-      <c r="AB17" s="4"/>
+      <c r="AB17" s="4">
+        <v>108</v>
+      </c>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9">
-        <v>1490</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2339,78 +2247,84 @@
         <v>22</v>
       </c>
       <c r="B18" s="6">
-        <v>1455</v>
+        <v>1384</v>
       </c>
       <c r="C18" s="6">
-        <v>1493</v>
+        <v>1437</v>
       </c>
       <c r="D18" s="6">
-        <v>999</v>
+        <v>933</v>
       </c>
       <c r="E18" s="6">
-        <v>997</v>
+        <v>961</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6">
-        <v>1244</v>
+        <v>1172</v>
       </c>
       <c r="H18" s="6">
-        <v>1383</v>
+        <v>1310</v>
       </c>
       <c r="I18" s="6">
-        <v>1172</v>
+        <v>1111</v>
       </c>
       <c r="J18" s="6">
-        <v>1292</v>
+        <v>1223</v>
       </c>
       <c r="K18" s="6">
-        <v>1440</v>
+        <v>1367</v>
       </c>
       <c r="L18" s="6">
-        <v>823</v>
-      </c>
-      <c r="M18" s="6">
-        <v>1127</v>
-      </c>
+        <v>777</v>
+      </c>
+      <c r="M18" s="6"/>
       <c r="N18" s="6">
-        <v>756</v>
+        <v>1052</v>
       </c>
       <c r="O18" s="6">
-        <v>793</v>
+        <v>1074</v>
       </c>
       <c r="P18" s="6">
-        <v>860</v>
+        <v>1136</v>
       </c>
       <c r="Q18" s="6">
-        <v>860</v>
+        <v>1355</v>
       </c>
       <c r="R18" s="6">
-        <v>727</v>
+        <v>695</v>
       </c>
       <c r="S18" s="6">
-        <v>1230</v>
-      </c>
-      <c r="T18" s="6">
-        <v>1657</v>
-      </c>
+        <v>1167</v>
+      </c>
+      <c r="T18" s="6"/>
       <c r="U18" s="6">
-        <v>1458</v>
+        <v>1575</v>
       </c>
       <c r="V18" s="6">
-        <v>1291</v>
-      </c>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
+        <v>1379</v>
+      </c>
+      <c r="W18" s="6">
+        <v>1258</v>
+      </c>
+      <c r="X18" s="6">
+        <v>1541</v>
+      </c>
+      <c r="Y18" s="6">
+        <v>846</v>
+      </c>
+      <c r="Z18" s="6">
+        <v>848</v>
+      </c>
       <c r="AA18" s="6"/>
-      <c r="AB18" s="6"/>
+      <c r="AB18" s="6">
+        <v>1217</v>
+      </c>
       <c r="AC18" s="6"/>
       <c r="AD18" s="6"/>
       <c r="AE18" s="6"/>
       <c r="AF18" s="6"/>
       <c r="AG18" s="10">
-        <v>22197</v>
+        <v>26818</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2483,7 +2397,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.1315789473684212</v>
+        <v>3.0027173913043477</v>
       </c>
     </row>
   </sheetData>

--- a/Juli-2026.xlsx
+++ b/Juli-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CB7A08-A810-4AA1-9C80-15F8C6B9E29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBC0EDC-3D3C-402E-836B-F93CA84CC07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,10 +566,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>282</v>
+        <v>433</v>
       </c>
       <c r="C2" s="4">
-        <v>566</v>
+        <v>1230</v>
       </c>
       <c r="D2" s="9">
         <v>73</v>
@@ -585,10 +585,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>284</v>
+        <v>409</v>
       </c>
       <c r="C3" s="4">
-        <v>613</v>
+        <v>1217</v>
       </c>
       <c r="D3" s="9">
         <v>65</v>
@@ -604,10 +604,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>265</v>
+        <v>430</v>
       </c>
       <c r="C4" s="4">
-        <v>570</v>
+        <v>1461</v>
       </c>
       <c r="D4" s="9">
         <v>66</v>
@@ -623,10 +623,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>300</v>
+        <v>464</v>
       </c>
       <c r="C5" s="4">
-        <v>598</v>
+        <v>1165</v>
       </c>
       <c r="D5" s="9">
         <v>88</v>
@@ -642,10 +642,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>300</v>
+        <v>431</v>
       </c>
       <c r="C6" s="4">
-        <v>586</v>
+        <v>1324</v>
       </c>
       <c r="D6" s="9">
         <v>74</v>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>372</v>
+        <v>551</v>
       </c>
       <c r="C7" s="4">
-        <v>662</v>
+        <v>1307</v>
       </c>
       <c r="D7" s="9">
         <v>110</v>
@@ -680,10 +680,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>316</v>
+        <v>439</v>
       </c>
       <c r="C8" s="4">
-        <v>631</v>
+        <v>1383</v>
       </c>
       <c r="D8" s="9">
         <v>87</v>
@@ -699,10 +699,10 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>300</v>
+        <v>372</v>
       </c>
       <c r="C9" s="4">
-        <v>619</v>
+        <v>1385</v>
       </c>
       <c r="D9" s="9">
         <v>78</v>
@@ -718,10 +718,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>337</v>
+        <v>452</v>
       </c>
       <c r="C10" s="4">
-        <v>463</v>
+        <v>1080</v>
       </c>
       <c r="D10" s="9">
         <v>82</v>
@@ -737,10 +737,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="C11" s="4">
-        <v>622</v>
+        <v>1133</v>
       </c>
       <c r="D11" s="9">
         <v>60</v>
@@ -756,10 +756,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>337</v>
+        <v>464</v>
       </c>
       <c r="C12" s="4">
-        <v>596</v>
+        <v>1252</v>
       </c>
       <c r="D12" s="9">
         <v>63</v>
@@ -775,10 +775,10 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>248</v>
+        <v>331</v>
       </c>
       <c r="C13" s="4">
-        <v>707</v>
+        <v>1217</v>
       </c>
       <c r="D13" s="9">
         <v>53</v>
@@ -794,10 +794,10 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="C14" s="4">
-        <v>659</v>
+        <v>1228</v>
       </c>
       <c r="D14" s="9">
         <v>45</v>
@@ -813,10 +813,10 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="C15" s="4">
-        <v>667</v>
+        <v>1488</v>
       </c>
       <c r="D15" s="9">
         <v>40</v>
@@ -832,10 +832,10 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>175</v>
+        <v>228</v>
       </c>
       <c r="C16" s="4">
-        <v>731</v>
+        <v>1350</v>
       </c>
       <c r="D16" s="9">
         <v>47</v>
@@ -851,10 +851,10 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>273</v>
+        <v>404</v>
       </c>
       <c r="C17" s="4">
-        <v>696</v>
+        <v>1420</v>
       </c>
       <c r="D17" s="9">
         <v>74</v>
@@ -870,10 +870,10 @@
         <v>22</v>
       </c>
       <c r="B18" s="6">
-        <v>4337</v>
+        <v>6178</v>
       </c>
       <c r="C18" s="6">
-        <v>9986</v>
+        <v>20640</v>
       </c>
       <c r="D18" s="10">
         <v>1105</v>

--- a/Juli-2026.xlsx
+++ b/Juli-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBC0EDC-3D3C-402E-836B-F93CA84CC07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA35A935-2F4A-4321-8500-5C960256A741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -566,16 +566,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>433</v>
+        <v>554</v>
       </c>
       <c r="C2" s="4">
-        <v>1230</v>
+        <v>1518</v>
       </c>
       <c r="D2" s="9">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E2" s="13">
-        <v>3.1739130434782608</v>
+        <v>3.4545454545454546</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -585,16 +585,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>409</v>
+        <v>559</v>
       </c>
       <c r="C3" s="4">
-        <v>1217</v>
+        <v>1537</v>
       </c>
       <c r="D3" s="9">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E3" s="13">
-        <v>2.8260869565217392</v>
+        <v>3.0909090909090908</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -604,16 +604,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>430</v>
+        <v>503</v>
       </c>
       <c r="C4" s="4">
-        <v>1461</v>
+        <v>1625</v>
       </c>
       <c r="D4" s="9">
         <v>66</v>
       </c>
       <c r="E4" s="13">
-        <v>2.8695652173913042</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -623,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>464</v>
+        <v>556</v>
       </c>
       <c r="C5" s="4">
-        <v>1165</v>
+        <v>1409</v>
       </c>
       <c r="D5" s="9">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E5" s="13">
-        <v>3.8260869565217392</v>
+        <v>4.1818181818181817</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -642,16 +642,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>431</v>
+        <v>548</v>
       </c>
       <c r="C6" s="4">
-        <v>1324</v>
+        <v>1670</v>
       </c>
       <c r="D6" s="9">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E6" s="13">
-        <v>3.2173913043478262</v>
+        <v>3.6818181818181817</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -661,16 +661,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="4">
-        <v>551</v>
+        <v>668</v>
       </c>
       <c r="C7" s="4">
-        <v>1307</v>
+        <v>1631</v>
       </c>
       <c r="D7" s="9">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E7" s="13">
-        <v>4.7826086956521738</v>
+        <v>5.2727272727272725</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -680,16 +680,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="4">
-        <v>439</v>
+        <v>566</v>
       </c>
       <c r="C8" s="4">
-        <v>1383</v>
+        <v>1720</v>
       </c>
       <c r="D8" s="9">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E8" s="13">
-        <v>3.7826086956521738</v>
+        <v>4.2272727272727275</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -699,16 +699,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="4">
-        <v>372</v>
+        <v>530</v>
       </c>
       <c r="C9" s="4">
-        <v>1385</v>
+        <v>1718</v>
       </c>
       <c r="D9" s="9">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E9" s="13">
-        <v>3.3913043478260869</v>
+        <v>3.7727272727272729</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -718,16 +718,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="4">
-        <v>452</v>
+        <v>616</v>
       </c>
       <c r="C10" s="4">
-        <v>1080</v>
+        <v>1372</v>
       </c>
       <c r="D10" s="9">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E10" s="13">
-        <v>3.5652173913043477</v>
+        <v>3.8181818181818183</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -737,16 +737,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>248</v>
+        <v>400</v>
       </c>
       <c r="C11" s="4">
-        <v>1133</v>
+        <v>1440</v>
       </c>
       <c r="D11" s="9">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E11" s="13">
-        <v>2.6086956521739131</v>
+        <v>2.9090909090909092</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -756,16 +756,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="4">
-        <v>464</v>
+        <v>614</v>
       </c>
       <c r="C12" s="4">
-        <v>1252</v>
+        <v>1596</v>
       </c>
       <c r="D12" s="9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E12" s="13">
-        <v>2.7391304347826089</v>
+        <v>2.9090909090909092</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -775,16 +775,16 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>331</v>
+        <v>414</v>
       </c>
       <c r="C13" s="4">
-        <v>1217</v>
+        <v>1474</v>
       </c>
       <c r="D13" s="9">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E13" s="13">
-        <v>2.3043478260869565</v>
+        <v>2.5909090909090908</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -794,16 +794,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>270</v>
+        <v>377</v>
       </c>
       <c r="C14" s="4">
-        <v>1228</v>
+        <v>1533</v>
       </c>
       <c r="D14" s="9">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E14" s="13">
-        <v>1.9565217391304348</v>
+        <v>2.3181818181818183</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -813,16 +813,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="4">
-        <v>252</v>
+        <v>359</v>
       </c>
       <c r="C15" s="4">
-        <v>1488</v>
+        <v>1839</v>
       </c>
       <c r="D15" s="9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E15" s="13">
-        <v>1.7391304347826086</v>
+        <v>1.8636363636363635</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -832,16 +832,16 @@
         <v>19</v>
       </c>
       <c r="B16" s="4">
-        <v>228</v>
+        <v>327</v>
       </c>
       <c r="C16" s="4">
-        <v>1350</v>
+        <v>1597</v>
       </c>
       <c r="D16" s="9">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E16" s="13">
-        <v>2.0434782608695654</v>
+        <v>2.3636363636363638</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -851,16 +851,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4">
-        <v>404</v>
+        <v>493</v>
       </c>
       <c r="C17" s="4">
-        <v>1420</v>
+        <v>1668</v>
       </c>
       <c r="D17" s="9">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E17" s="13">
-        <v>3.2173913043478262</v>
+        <v>3.5</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -870,16 +870,16 @@
         <v>22</v>
       </c>
       <c r="B18" s="6">
-        <v>6178</v>
+        <v>8084</v>
       </c>
       <c r="C18" s="6">
-        <v>20640</v>
+        <v>25347</v>
       </c>
       <c r="D18" s="10">
-        <v>1105</v>
+        <v>1165</v>
       </c>
       <c r="E18" s="14">
-        <v>3.0027173913043477</v>
+        <v>3.3096590909090908</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -1077,7 +1077,9 @@
       <c r="B2" s="4">
         <v>97</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
       <c r="D2" s="4">
         <v>74</v>
       </c>
@@ -1097,8 +1099,12 @@
       <c r="J2" s="4">
         <v>84</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <v>94</v>
@@ -1106,11 +1112,15 @@
       <c r="O2" s="4">
         <v>99</v>
       </c>
-      <c r="P2" s="4"/>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
       <c r="Q2" s="4">
         <v>97</v>
       </c>
-      <c r="R2" s="4"/>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
       <c r="S2" s="4">
         <v>99</v>
       </c>
@@ -1130,17 +1140,27 @@
       <c r="Y2" s="4">
         <v>102</v>
       </c>
-      <c r="Z2" s="4"/>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4">
         <v>93</v>
       </c>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
+      <c r="AC2" s="4">
+        <v>106</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>98</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>98</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>107</v>
+      </c>
       <c r="AG2" s="9">
-        <v>1663</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1156,7 +1176,9 @@
       <c r="D3" s="4">
         <v>53</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
         <v>81</v>
@@ -1167,7 +1189,9 @@
       <c r="I3" s="4">
         <v>78</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
       <c r="K3" s="4">
         <v>112</v>
       </c>
@@ -1175,15 +1199,21 @@
         <v>80</v>
       </c>
       <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
       <c r="O3" s="4">
         <v>106</v>
       </c>
       <c r="P3" s="4">
         <v>103</v>
       </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
       <c r="S3" s="4">
         <v>112</v>
       </c>
@@ -1191,7 +1221,9 @@
       <c r="U3" s="4">
         <v>107</v>
       </c>
-      <c r="V3" s="4"/>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
       <c r="W3" s="4">
         <v>108</v>
       </c>
@@ -1208,12 +1240,20 @@
       <c r="AB3" s="4">
         <v>90</v>
       </c>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="4"/>
+      <c r="AC3" s="4">
+        <v>126</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>114</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>111</v>
+      </c>
+      <c r="AF3" s="4">
+        <v>119</v>
+      </c>
       <c r="AG3" s="9">
-        <v>1626</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -1223,7 +1263,9 @@
       <c r="B4" s="4">
         <v>131</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
       <c r="D4" s="4">
         <v>100</v>
       </c>
@@ -1246,7 +1288,9 @@
       <c r="K4" s="4">
         <v>111</v>
       </c>
-      <c r="L4" s="4"/>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4">
         <v>110</v>
@@ -1254,7 +1298,9 @@
       <c r="O4" s="4">
         <v>104</v>
       </c>
-      <c r="P4" s="4"/>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
       <c r="Q4" s="4">
         <v>100</v>
       </c>
@@ -1277,7 +1323,9 @@
       <c r="X4" s="4">
         <v>99</v>
       </c>
-      <c r="Y4" s="4"/>
+      <c r="Y4" s="4">
+        <v>0</v>
+      </c>
       <c r="Z4" s="4">
         <v>108</v>
       </c>
@@ -1285,12 +1333,20 @@
       <c r="AB4" s="4">
         <v>13</v>
       </c>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
+      <c r="AC4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>125</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>112</v>
+      </c>
+      <c r="AF4" s="4">
+        <v>0</v>
+      </c>
       <c r="AG4" s="9">
-        <v>1891</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -1306,9 +1362,13 @@
       <c r="D5" s="4">
         <v>46</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
       <c r="H5" s="4">
         <v>100</v>
       </c>
@@ -1325,13 +1385,21 @@
         <v>98</v>
       </c>
       <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
       <c r="Q5" s="4">
         <v>93</v>
       </c>
-      <c r="R5" s="4"/>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
       <c r="S5" s="4">
         <v>115</v>
       </c>
@@ -1342,7 +1410,9 @@
       <c r="V5" s="4">
         <v>105</v>
       </c>
-      <c r="W5" s="4"/>
+      <c r="W5" s="4">
+        <v>0</v>
+      </c>
       <c r="X5" s="4">
         <v>108</v>
       </c>
@@ -1356,12 +1426,20 @@
       <c r="AB5" s="4">
         <v>97</v>
       </c>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
-      <c r="AF5" s="4"/>
+      <c r="AC5" s="4">
+        <v>119</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>105</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>112</v>
+      </c>
+      <c r="AF5" s="4">
+        <v>0</v>
+      </c>
       <c r="AG5" s="9">
-        <v>1629</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -1387,7 +1465,9 @@
       <c r="H6" s="4">
         <v>1</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
       <c r="J6" s="4">
         <v>91</v>
       </c>
@@ -1398,7 +1478,9 @@
         <v>98</v>
       </c>
       <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
       <c r="O6" s="4">
         <v>99</v>
       </c>
@@ -1427,18 +1509,30 @@
       <c r="X6" s="4">
         <v>100</v>
       </c>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>0</v>
+      </c>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4">
         <v>108</v>
       </c>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
-      <c r="AE6" s="4"/>
-      <c r="AF6" s="4"/>
+      <c r="AC6" s="4">
+        <v>115</v>
+      </c>
+      <c r="AD6" s="4">
+        <v>112</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>112</v>
+      </c>
+      <c r="AF6" s="4">
+        <v>124</v>
+      </c>
       <c r="AG6" s="9">
-        <v>1755</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -1454,12 +1548,16 @@
       <c r="D7" s="4">
         <v>58</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
         <v>119</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
       <c r="I7" s="4">
         <v>112</v>
       </c>
@@ -1498,11 +1596,15 @@
       <c r="V7" s="4">
         <v>111</v>
       </c>
-      <c r="W7" s="4"/>
+      <c r="W7" s="4">
+        <v>0</v>
+      </c>
       <c r="X7" s="4">
         <v>109</v>
       </c>
-      <c r="Y7" s="4"/>
+      <c r="Y7" s="4">
+        <v>0</v>
+      </c>
       <c r="Z7" s="4">
         <v>103</v>
       </c>
@@ -1510,12 +1612,20 @@
       <c r="AB7" s="4">
         <v>103</v>
       </c>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
-      <c r="AF7" s="4"/>
+      <c r="AC7" s="4">
+        <v>111</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>118</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>107</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>105</v>
+      </c>
       <c r="AG7" s="9">
-        <v>1858</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1528,12 +1638,16 @@
       <c r="C8" s="4">
         <v>100</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
       <c r="E8" s="4">
         <v>117</v>
       </c>
       <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
       <c r="H8" s="4">
         <v>131</v>
       </c>
@@ -1546,19 +1660,25 @@
       <c r="K8" s="4">
         <v>100</v>
       </c>
-      <c r="L8" s="4"/>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
       <c r="M8" s="4"/>
       <c r="N8" s="4">
         <v>90</v>
       </c>
-      <c r="O8" s="4"/>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
       <c r="P8" s="4">
         <v>98</v>
       </c>
       <c r="Q8" s="4">
         <v>109</v>
       </c>
-      <c r="R8" s="4"/>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
       <c r="S8" s="4">
         <v>101</v>
       </c>
@@ -1578,17 +1698,27 @@
       <c r="Y8" s="4">
         <v>138</v>
       </c>
-      <c r="Z8" s="4"/>
+      <c r="Z8" s="4">
+        <v>0</v>
+      </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4">
         <v>105</v>
       </c>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
-      <c r="AF8" s="4"/>
+      <c r="AC8" s="4">
+        <v>115</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>112</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>113</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>124</v>
+      </c>
       <c r="AG8" s="9">
-        <v>1822</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1601,7 +1731,9 @@
       <c r="C9" s="4">
         <v>127</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
       <c r="E9" s="4">
         <v>132</v>
       </c>
@@ -1618,7 +1750,9 @@
       <c r="J9" s="4">
         <v>86</v>
       </c>
-      <c r="K9" s="4"/>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
       <c r="L9" s="4">
         <v>85</v>
       </c>
@@ -1626,7 +1760,9 @@
       <c r="N9" s="4">
         <v>102</v>
       </c>
-      <c r="O9" s="4"/>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
       <c r="P9" s="4">
         <v>103</v>
       </c>
@@ -1636,7 +1772,9 @@
       <c r="R9" s="4">
         <v>92</v>
       </c>
-      <c r="S9" s="4"/>
+      <c r="S9" s="4">
+        <v>0</v>
+      </c>
       <c r="T9" s="4"/>
       <c r="U9" s="4">
         <v>108</v>
@@ -1650,18 +1788,30 @@
       <c r="X9" s="4">
         <v>96</v>
       </c>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
+      <c r="Y9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>0</v>
+      </c>
       <c r="AA9" s="4"/>
       <c r="AB9" s="4">
         <v>97</v>
       </c>
-      <c r="AC9" s="4"/>
-      <c r="AD9" s="4"/>
-      <c r="AE9" s="4"/>
-      <c r="AF9" s="4"/>
+      <c r="AC9" s="4">
+        <v>119</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>128</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>121</v>
+      </c>
+      <c r="AF9" s="4">
+        <v>123</v>
+      </c>
       <c r="AG9" s="9">
-        <v>1757</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1677,13 +1827,19 @@
       <c r="D10" s="4">
         <v>57</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4">
         <v>91</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
       <c r="J10" s="4">
         <v>103</v>
       </c>
@@ -1703,7 +1859,9 @@
       <c r="P10" s="4">
         <v>100</v>
       </c>
-      <c r="Q10" s="4"/>
+      <c r="Q10" s="4">
+        <v>0</v>
+      </c>
       <c r="R10" s="4">
         <v>115</v>
       </c>
@@ -1711,26 +1869,42 @@
         <v>106</v>
       </c>
       <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
+      <c r="U10" s="4">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4">
+        <v>0</v>
+      </c>
       <c r="W10" s="4">
         <v>106</v>
       </c>
       <c r="X10" s="4">
         <v>103</v>
       </c>
-      <c r="Y10" s="4"/>
+      <c r="Y10" s="4">
+        <v>0</v>
+      </c>
       <c r="Z10" s="4">
         <v>102</v>
       </c>
       <c r="AA10" s="4"/>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
-      <c r="AF10" s="4"/>
+      <c r="AB10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>114</v>
+      </c>
+      <c r="AD10" s="4">
+        <v>123</v>
+      </c>
+      <c r="AE10" s="4">
+        <v>107</v>
+      </c>
+      <c r="AF10" s="4">
+        <v>112</v>
+      </c>
       <c r="AG10" s="9">
-        <v>1532</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1740,7 +1914,9 @@
       <c r="B11" s="4">
         <v>89</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
       <c r="D11" s="4">
         <v>56</v>
       </c>
@@ -1763,7 +1939,9 @@
       <c r="K11" s="4">
         <v>78</v>
       </c>
-      <c r="L11" s="4"/>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4">
         <v>97</v>
@@ -1774,7 +1952,9 @@
       <c r="P11" s="4">
         <v>96</v>
       </c>
-      <c r="Q11" s="4"/>
+      <c r="Q11" s="4">
+        <v>0</v>
+      </c>
       <c r="R11" s="4">
         <v>62</v>
       </c>
@@ -1794,16 +1974,30 @@
       <c r="X11" s="4">
         <v>5</v>
       </c>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
+      <c r="Y11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>0</v>
+      </c>
       <c r="AA11" s="4"/>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
-      <c r="AF11" s="4"/>
+      <c r="AB11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>85</v>
+      </c>
+      <c r="AD11" s="4">
+        <v>121</v>
+      </c>
+      <c r="AE11" s="4">
+        <v>123</v>
+      </c>
+      <c r="AF11" s="4">
+        <v>130</v>
+      </c>
       <c r="AG11" s="9">
-        <v>1381</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
@@ -1819,7 +2013,9 @@
       <c r="D12" s="4">
         <v>92</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
         <v>105</v>
@@ -1827,14 +2023,18 @@
       <c r="H12" s="4">
         <v>108</v>
       </c>
-      <c r="I12" s="4"/>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
       <c r="J12" s="4">
         <v>100</v>
       </c>
       <c r="K12" s="4">
         <v>99</v>
       </c>
-      <c r="L12" s="4"/>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4">
         <v>15</v>
@@ -1848,7 +2048,9 @@
       <c r="Q12" s="4">
         <v>107</v>
       </c>
-      <c r="R12" s="4"/>
+      <c r="R12" s="4">
+        <v>0</v>
+      </c>
       <c r="S12" s="4">
         <v>111</v>
       </c>
@@ -1859,24 +2061,36 @@
       <c r="V12" s="4">
         <v>105</v>
       </c>
-      <c r="W12" s="4"/>
+      <c r="W12" s="4">
+        <v>0</v>
+      </c>
       <c r="X12" s="4">
         <v>107</v>
       </c>
       <c r="Y12" s="4">
         <v>120</v>
       </c>
-      <c r="Z12" s="4"/>
+      <c r="Z12" s="4">
+        <v>0</v>
+      </c>
       <c r="AA12" s="4"/>
       <c r="AB12" s="4">
         <v>97</v>
       </c>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="4"/>
+      <c r="AC12" s="4">
+        <v>122</v>
+      </c>
+      <c r="AD12" s="4">
+        <v>119</v>
+      </c>
+      <c r="AE12" s="4">
+        <v>124</v>
+      </c>
+      <c r="AF12" s="4">
+        <v>129</v>
+      </c>
       <c r="AG12" s="9">
-        <v>1716</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1892,7 +2106,9 @@
       <c r="D13" s="4">
         <v>72</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4">
         <v>79</v>
@@ -1903,7 +2119,9 @@
       <c r="I13" s="4">
         <v>96</v>
       </c>
-      <c r="J13" s="4"/>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
       <c r="K13" s="4">
         <v>101</v>
       </c>
@@ -1914,7 +2132,9 @@
       <c r="N13" s="4">
         <v>126</v>
       </c>
-      <c r="O13" s="4"/>
+      <c r="O13" s="4">
+        <v>0</v>
+      </c>
       <c r="P13" s="4">
         <v>8</v>
       </c>
@@ -1931,12 +2151,18 @@
       <c r="U13" s="4">
         <v>101</v>
       </c>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
+      <c r="V13" s="4">
+        <v>0</v>
+      </c>
+      <c r="W13" s="4">
+        <v>0</v>
+      </c>
       <c r="X13" s="4">
         <v>103</v>
       </c>
-      <c r="Y13" s="4"/>
+      <c r="Y13" s="4">
+        <v>0</v>
+      </c>
       <c r="Z13" s="4">
         <v>113</v>
       </c>
@@ -1944,12 +2170,20 @@
       <c r="AB13" s="4">
         <v>94</v>
       </c>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="4"/>
-      <c r="AF13" s="4"/>
+      <c r="AC13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="4">
+        <v>106</v>
+      </c>
+      <c r="AE13" s="4">
+        <v>126</v>
+      </c>
+      <c r="AF13" s="4">
+        <v>108</v>
+      </c>
       <c r="AG13" s="9">
-        <v>1548</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1962,12 +2196,16 @@
       <c r="C14" s="4">
         <v>107</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
       <c r="E14" s="4">
         <v>97</v>
       </c>
       <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
       <c r="H14" s="4">
         <v>93</v>
       </c>
@@ -1980,18 +2218,28 @@
       <c r="K14" s="4">
         <v>98</v>
       </c>
-      <c r="L14" s="4"/>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
       <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
       <c r="P14" s="4">
         <v>103</v>
       </c>
       <c r="Q14" s="4">
         <v>99</v>
       </c>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0</v>
+      </c>
       <c r="T14" s="4"/>
       <c r="U14" s="4">
         <v>97</v>
@@ -2008,17 +2256,27 @@
       <c r="Y14" s="4">
         <v>106</v>
       </c>
-      <c r="Z14" s="4"/>
+      <c r="Z14" s="4">
+        <v>0</v>
+      </c>
       <c r="AA14" s="4"/>
       <c r="AB14" s="4">
         <v>102</v>
       </c>
-      <c r="AC14" s="4"/>
-      <c r="AD14" s="4"/>
-      <c r="AE14" s="4"/>
-      <c r="AF14" s="4"/>
+      <c r="AC14" s="4">
+        <v>119</v>
+      </c>
+      <c r="AD14" s="4">
+        <v>57</v>
+      </c>
+      <c r="AE14" s="4">
+        <v>109</v>
+      </c>
+      <c r="AF14" s="4">
+        <v>127</v>
+      </c>
       <c r="AG14" s="9">
-        <v>1498</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -2034,7 +2292,9 @@
       <c r="D15" s="4">
         <v>86</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
         <v>101</v>
@@ -2042,7 +2302,9 @@
       <c r="H15" s="4">
         <v>108</v>
       </c>
-      <c r="I15" s="4"/>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
       <c r="J15" s="4">
         <v>91</v>
       </c>
@@ -2059,11 +2321,15 @@
       <c r="O15" s="4">
         <v>103</v>
       </c>
-      <c r="P15" s="4"/>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
       <c r="Q15" s="4">
         <v>99</v>
       </c>
-      <c r="R15" s="4"/>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
       <c r="S15" s="4">
         <v>99</v>
       </c>
@@ -2083,15 +2349,27 @@
       <c r="Y15" s="4">
         <v>127</v>
       </c>
-      <c r="Z15" s="4"/>
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
       <c r="AA15" s="4"/>
-      <c r="AB15" s="4"/>
-      <c r="AC15" s="4"/>
-      <c r="AD15" s="4"/>
-      <c r="AE15" s="4"/>
-      <c r="AF15" s="4"/>
+      <c r="AB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>125</v>
+      </c>
+      <c r="AD15" s="4">
+        <v>110</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>107</v>
+      </c>
+      <c r="AF15" s="4">
+        <v>116</v>
+      </c>
       <c r="AG15" s="9">
-        <v>1740</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -2107,7 +2385,9 @@
       <c r="D16" s="4">
         <v>64</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
         <v>110</v>
@@ -2118,7 +2398,9 @@
       <c r="I16" s="4">
         <v>76</v>
       </c>
-      <c r="J16" s="4"/>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
       <c r="K16" s="4">
         <v>92</v>
       </c>
@@ -2126,7 +2408,9 @@
         <v>78</v>
       </c>
       <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
       <c r="O16" s="4">
         <v>50</v>
       </c>
@@ -2136,8 +2420,12 @@
       <c r="Q16" s="4">
         <v>111</v>
       </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
       <c r="T16" s="4"/>
       <c r="U16" s="4">
         <v>105</v>
@@ -2151,7 +2439,9 @@
       <c r="X16" s="4">
         <v>106</v>
       </c>
-      <c r="Y16" s="4"/>
+      <c r="Y16" s="4">
+        <v>0</v>
+      </c>
       <c r="Z16" s="4">
         <v>112</v>
       </c>
@@ -2159,19 +2449,29 @@
       <c r="AB16" s="4">
         <v>110</v>
       </c>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
-      <c r="AE16" s="4"/>
-      <c r="AF16" s="4"/>
+      <c r="AC16" s="4">
+        <v>87</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>11</v>
+      </c>
+      <c r="AE16" s="4">
+        <v>115</v>
+      </c>
+      <c r="AF16" s="4">
+        <v>133</v>
+      </c>
       <c r="AG16" s="9">
-        <v>1578</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="4"/>
+      <c r="B17" s="4">
+        <v>0</v>
+      </c>
       <c r="C17" s="4">
         <v>108</v>
       </c>
@@ -2197,7 +2497,9 @@
       <c r="K17" s="4">
         <v>102</v>
       </c>
-      <c r="L17" s="4"/>
+      <c r="L17" s="4">
+        <v>0</v>
+      </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4">
         <v>111</v>
@@ -2211,8 +2513,12 @@
       <c r="Q17" s="4">
         <v>100</v>
       </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4">
+        <v>0</v>
+      </c>
       <c r="T17" s="4"/>
       <c r="U17" s="4">
         <v>106</v>
@@ -2226,7 +2532,9 @@
       <c r="X17" s="4">
         <v>100</v>
       </c>
-      <c r="Y17" s="4"/>
+      <c r="Y17" s="4">
+        <v>0</v>
+      </c>
       <c r="Z17" s="4">
         <v>105</v>
       </c>
@@ -2234,12 +2542,20 @@
       <c r="AB17" s="4">
         <v>108</v>
       </c>
-      <c r="AC17" s="4"/>
-      <c r="AD17" s="4"/>
-      <c r="AE17" s="4"/>
-      <c r="AF17" s="4"/>
+      <c r="AC17" s="4">
+        <v>115</v>
+      </c>
+      <c r="AD17" s="4">
+        <v>111</v>
+      </c>
+      <c r="AE17" s="4">
+        <v>111</v>
+      </c>
+      <c r="AF17" s="4">
+        <v>0</v>
+      </c>
       <c r="AG17" s="9">
-        <v>1824</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -2319,12 +2635,20 @@
       <c r="AB18" s="6">
         <v>1217</v>
       </c>
-      <c r="AC18" s="6"/>
-      <c r="AD18" s="6"/>
-      <c r="AE18" s="6"/>
-      <c r="AF18" s="6"/>
+      <c r="AC18" s="6">
+        <v>1578</v>
+      </c>
+      <c r="AD18" s="6">
+        <v>1670</v>
+      </c>
+      <c r="AE18" s="6">
+        <v>1808</v>
+      </c>
+      <c r="AF18" s="6">
+        <v>1557</v>
+      </c>
       <c r="AG18" s="10">
-        <v>26818</v>
+        <v>33431</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -2397,7 +2721,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.0027173913043477</v>
+        <v>3.3096590909090908</v>
       </c>
     </row>
   </sheetData>
